--- a/tools/excel/netherlands/abro_2026.xlsx
+++ b/tools/excel/netherlands/abro_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\netherlands\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3743659A-F351-4768-B427-DB251C7F17E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646AA5B0-F82C-4122-AE3B-B43CF2A0D982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="-15870" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-17700" windowWidth="46296" windowHeight="26136" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -3766,9 +3766,6 @@
     <t>All Special Information located outside the designated physical Compartment must be encrypted using Approved Means.</t>
   </si>
   <si>
-    <t>4.1-2</t>
-  </si>
-  <si>
     <t>Kwetsbaarheden- en patchmanagement</t>
   </si>
   <si>
@@ -4582,6 +4579,9 @@
 Bron :
 * https://open.overheid.nl/documenten/a13699d9-fcf4-43ef-b282-ece9519e9b81/file
 * https://open.overheid.nl/documenten/8a2c1e3a-f62c-4cd6-9827-3d4ccc9162ba/file</t>
+  </si>
+  <si>
+    <t>4.10</t>
   </si>
 </sst>
 </file>
@@ -4634,6 +4634,7 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4696,25 +4697,25 @@
   <autoFilter ref="A1:H493" xr:uid="{73681CBD-8DCB-4DB1-8FFD-341893D516A9}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{A9A6AE71-9491-4F12-9E0F-1001D394508B}" name="assessable" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{2B794E5B-6917-45B7-947B-B42A0DC7D060}" name="depth" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{6A3FF142-C8B8-4D40-8649-FC882E6050B3}" name="ref_id" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{8DEB4632-BBBF-4EBA-8A9E-16B024982EBA}" name="name" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{EAC09B15-5C3A-4874-AD37-FDFC41851BB8}" name="description" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{7A124031-6732-40FE-AB86-5603396EC7F4}" name="implementation_groups" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{5C573CB3-7CC8-4914-B9E9-B0951D2187AE}" name="name[en]" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{4CE7D482-B6D2-45FA-9458-4315F01DE0DF}" name="description[en]" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{2B794E5B-6917-45B7-947B-B42A0DC7D060}" name="depth" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{6A3FF142-C8B8-4D40-8649-FC882E6050B3}" name="ref_id" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{8DEB4632-BBBF-4EBA-8A9E-16B024982EBA}" name="name" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{EAC09B15-5C3A-4874-AD37-FDFC41851BB8}" name="description" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{7A124031-6732-40FE-AB86-5603396EC7F4}" name="implementation_groups" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{5C573CB3-7CC8-4914-B9E9-B0951D2187AE}" name="name[en]" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{4CE7D482-B6D2-45FA-9458-4315F01DE0DF}" name="description[en]" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8D147901-084A-48DC-AAC9-9F1D4D9C0F98}" name="Tableau2" displayName="Tableau2" ref="A1:C5" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8D147901-084A-48DC-AAC9-9F1D4D9C0F98}" name="Tableau2" displayName="Tableau2" ref="A1:C5" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:C5" xr:uid="{8D147901-084A-48DC-AAC9-9F1D4D9C0F98}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BBCC19AB-94DC-428D-9609-2C1933428F00}" name="ref_id" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{8F507444-EC6F-43E8-B29C-644D77571FC2}" name="name" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{99A2D72D-1F7D-44F9-83DE-DB91412B745E}" name="name[en]" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{BBCC19AB-94DC-428D-9609-2C1933428F00}" name="ref_id" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{8F507444-EC6F-43E8-B29C-644D77571FC2}" name="name" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{99A2D72D-1F7D-44F9-83DE-DB91412B745E}" name="name[en]" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5065,7 +5066,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
@@ -5105,7 +5106,7 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
   </sheetData>
@@ -5167,7 +5168,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -5191,7 +5192,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
   </sheetData>
@@ -5245,7 +5246,7 @@
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -5263,7 +5264,7 @@
       <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -5283,7 +5284,7 @@
       <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D4" s="1"/>
@@ -5305,7 +5306,7 @@
       <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="1"/>
@@ -5327,7 +5328,7 @@
       <c r="B6" s="1">
         <v>3</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="1"/>
@@ -5349,7 +5350,7 @@
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D7" s="1"/>
@@ -5371,7 +5372,7 @@
       <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D8" s="1"/>
@@ -5393,7 +5394,7 @@
       <c r="B9" s="1">
         <v>3</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="1"/>
@@ -5415,7 +5416,7 @@
       <c r="B10" s="1">
         <v>3</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="1"/>
@@ -5437,7 +5438,7 @@
       <c r="B11" s="1">
         <v>3</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D11" s="1"/>
@@ -5459,7 +5460,7 @@
       <c r="B12" s="1">
         <v>3</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D12" s="1"/>
@@ -5481,7 +5482,7 @@
       <c r="B13" s="1">
         <v>3</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D13" s="1"/>
@@ -5503,7 +5504,7 @@
       <c r="B14" s="1">
         <v>3</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="1"/>
@@ -5525,7 +5526,7 @@
       <c r="B15" s="1">
         <v>3</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D15" s="1"/>
@@ -5547,7 +5548,7 @@
       <c r="B16" s="1">
         <v>3</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D16" s="1"/>
@@ -5569,7 +5570,7 @@
       <c r="B17" s="1">
         <v>3</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D17" s="1"/>
@@ -5591,7 +5592,7 @@
       <c r="B18" s="1">
         <v>3</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D18" s="1"/>
@@ -5613,7 +5614,7 @@
       <c r="B19" s="1">
         <v>3</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D19" s="1"/>
@@ -5635,7 +5636,7 @@
       <c r="B20" s="1">
         <v>3</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D20" s="1"/>
@@ -5655,7 +5656,7 @@
       <c r="B21" s="1">
         <v>2</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -5675,7 +5676,7 @@
       <c r="B22" s="1">
         <v>3</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D22" s="1"/>
@@ -5697,7 +5698,7 @@
       <c r="B23" s="1">
         <v>3</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D23" s="1"/>
@@ -5719,7 +5720,7 @@
       <c r="B24" s="1">
         <v>3</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D24" s="1"/>
@@ -5741,7 +5742,7 @@
       <c r="B25" s="1">
         <v>3</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D25" s="1"/>
@@ -5763,7 +5764,7 @@
       <c r="B26" s="1">
         <v>3</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D26" s="1"/>
@@ -5785,7 +5786,7 @@
       <c r="B27" s="1">
         <v>3</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D27" s="1"/>
@@ -5807,7 +5808,7 @@
       <c r="B28" s="1">
         <v>3</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D28" s="1"/>
@@ -5829,7 +5830,7 @@
       <c r="B29" s="1">
         <v>3</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D29" s="1"/>
@@ -5851,7 +5852,7 @@
       <c r="B30" s="1">
         <v>3</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D30" s="1"/>
@@ -5871,7 +5872,7 @@
       <c r="B31" s="1">
         <v>2</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -5891,7 +5892,7 @@
       <c r="B32" s="1">
         <v>3</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D32" s="1"/>
@@ -5913,7 +5914,7 @@
       <c r="B33" s="1">
         <v>3</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>126</v>
       </c>
       <c r="D33" s="1"/>
@@ -5935,7 +5936,7 @@
       <c r="B34" s="1">
         <v>3</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D34" s="1"/>
@@ -5957,7 +5958,7 @@
       <c r="B35" s="1">
         <v>3</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>132</v>
       </c>
       <c r="D35" s="1"/>
@@ -5979,7 +5980,7 @@
       <c r="B36" s="1">
         <v>3</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>135</v>
       </c>
       <c r="D36" s="1"/>
@@ -6001,7 +6002,7 @@
       <c r="B37" s="1">
         <v>3</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D37" s="1"/>
@@ -6023,7 +6024,7 @@
       <c r="B38" s="1">
         <v>3</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D38" s="1"/>
@@ -6045,7 +6046,7 @@
       <c r="B39" s="1">
         <v>3</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>144</v>
       </c>
       <c r="D39" s="1"/>
@@ -6067,7 +6068,7 @@
       <c r="B40" s="1">
         <v>3</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>147</v>
       </c>
       <c r="D40" s="1"/>
@@ -6087,7 +6088,7 @@
       <c r="B41" s="1">
         <v>2</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>150</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -6107,7 +6108,7 @@
       <c r="B42" s="1">
         <v>3</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>153</v>
       </c>
       <c r="D42" s="1"/>
@@ -6129,7 +6130,7 @@
       <c r="B43" s="1">
         <v>3</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>156</v>
       </c>
       <c r="D43" s="1"/>
@@ -6151,7 +6152,7 @@
       <c r="B44" s="1">
         <v>3</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D44" s="1"/>
@@ -6173,7 +6174,7 @@
       <c r="B45" s="1">
         <v>3</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>162</v>
       </c>
       <c r="D45" s="1"/>
@@ -6195,7 +6196,7 @@
       <c r="B46" s="1">
         <v>3</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>165</v>
       </c>
       <c r="D46" s="1"/>
@@ -6217,7 +6218,7 @@
       <c r="B47" s="1">
         <v>3</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D47" s="1"/>
@@ -6237,7 +6238,7 @@
       <c r="B48" s="1">
         <v>2</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>171</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -6257,7 +6258,7 @@
       <c r="B49" s="1">
         <v>3</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>174</v>
       </c>
       <c r="D49" s="1"/>
@@ -6279,7 +6280,7 @@
       <c r="B50" s="1">
         <v>3</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>177</v>
       </c>
       <c r="D50" s="1"/>
@@ -6301,7 +6302,7 @@
       <c r="B51" s="1">
         <v>3</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>180</v>
       </c>
       <c r="D51" s="1"/>
@@ -6323,7 +6324,7 @@
       <c r="B52" s="1">
         <v>3</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>183</v>
       </c>
       <c r="D52" s="1"/>
@@ -6345,7 +6346,7 @@
       <c r="B53" s="1">
         <v>3</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="2" t="s">
         <v>186</v>
       </c>
       <c r="D53" s="1"/>
@@ -6367,7 +6368,7 @@
       <c r="B54" s="1">
         <v>3</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>189</v>
       </c>
       <c r="D54" s="1"/>
@@ -6389,7 +6390,7 @@
       <c r="B55" s="1">
         <v>3</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>192</v>
       </c>
       <c r="D55" s="1"/>
@@ -6411,7 +6412,7 @@
       <c r="B56" s="1">
         <v>3</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D56" s="1"/>
@@ -6433,7 +6434,7 @@
       <c r="B57" s="1">
         <v>3</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>198</v>
       </c>
       <c r="D57" s="1"/>
@@ -6455,7 +6456,7 @@
       <c r="B58" s="1">
         <v>3</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="2" t="s">
         <v>201</v>
       </c>
       <c r="D58" s="1"/>
@@ -6475,7 +6476,7 @@
       <c r="B59" s="1">
         <v>2</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>204</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -6495,7 +6496,7 @@
       <c r="B60" s="1">
         <v>3</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>207</v>
       </c>
       <c r="D60" s="1"/>
@@ -6517,7 +6518,7 @@
       <c r="B61" s="1">
         <v>3</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="2" t="s">
         <v>210</v>
       </c>
       <c r="D61" s="1"/>
@@ -6539,7 +6540,7 @@
       <c r="B62" s="1">
         <v>3</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="2" t="s">
         <v>213</v>
       </c>
       <c r="D62" s="1"/>
@@ -6559,7 +6560,7 @@
       <c r="B63" s="1">
         <v>2</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="2" t="s">
         <v>216</v>
       </c>
       <c r="D63" s="1" t="s">
@@ -6579,7 +6580,7 @@
       <c r="B64" s="1">
         <v>3</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="2" t="s">
         <v>219</v>
       </c>
       <c r="D64" s="1"/>
@@ -6601,7 +6602,7 @@
       <c r="B65" s="1">
         <v>3</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="2" t="s">
         <v>222</v>
       </c>
       <c r="D65" s="1"/>
@@ -6623,7 +6624,7 @@
       <c r="B66" s="1">
         <v>3</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="2" t="s">
         <v>225</v>
       </c>
       <c r="D66" s="1"/>
@@ -6645,7 +6646,7 @@
       <c r="B67" s="1">
         <v>3</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="2" t="s">
         <v>228</v>
       </c>
       <c r="D67" s="1"/>
@@ -6667,7 +6668,7 @@
       <c r="B68" s="1">
         <v>3</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="2" t="s">
         <v>232</v>
       </c>
       <c r="D68" s="1"/>
@@ -6689,7 +6690,7 @@
       <c r="B69" s="1">
         <v>3</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D69" s="1"/>
@@ -6711,7 +6712,7 @@
       <c r="B70" s="1">
         <v>3</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="2" t="s">
         <v>239</v>
       </c>
       <c r="D70" s="1"/>
@@ -6733,7 +6734,7 @@
       <c r="B71" s="1">
         <v>3</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D71" s="1"/>
@@ -6755,7 +6756,7 @@
       <c r="B72" s="1">
         <v>3</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="2" t="s">
         <v>245</v>
       </c>
       <c r="D72" s="1"/>
@@ -6775,7 +6776,7 @@
       <c r="B73" s="1">
         <v>1</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="2" t="s">
         <v>248</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -6793,7 +6794,7 @@
       <c r="B74" s="1">
         <v>2</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="2" t="s">
         <v>251</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -6813,7 +6814,7 @@
       <c r="B75" s="1">
         <v>3</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="2" t="s">
         <v>254</v>
       </c>
       <c r="D75" s="1"/>
@@ -6835,7 +6836,7 @@
       <c r="B76" s="1">
         <v>3</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="2" t="s">
         <v>258</v>
       </c>
       <c r="D76" s="1"/>
@@ -6857,7 +6858,7 @@
       <c r="B77" s="1">
         <v>3</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="2" t="s">
         <v>261</v>
       </c>
       <c r="D77" s="1"/>
@@ -6879,7 +6880,7 @@
       <c r="B78" s="1">
         <v>3</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="2" t="s">
         <v>264</v>
       </c>
       <c r="D78" s="1"/>
@@ -6901,7 +6902,7 @@
       <c r="B79" s="1">
         <v>3</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="2" t="s">
         <v>267</v>
       </c>
       <c r="D79" s="1"/>
@@ -6923,7 +6924,7 @@
       <c r="B80" s="1">
         <v>3</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="2" t="s">
         <v>270</v>
       </c>
       <c r="D80" s="1"/>
@@ -6945,7 +6946,7 @@
       <c r="B81" s="1">
         <v>3</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="2" t="s">
         <v>273</v>
       </c>
       <c r="D81" s="1"/>
@@ -6967,7 +6968,7 @@
       <c r="B82" s="1">
         <v>3</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="2" t="s">
         <v>276</v>
       </c>
       <c r="D82" s="1"/>
@@ -6987,7 +6988,7 @@
       <c r="B83" s="1">
         <v>2</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="2" t="s">
         <v>279</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -7007,7 +7008,7 @@
       <c r="B84" s="1">
         <v>3</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="2" t="s">
         <v>282</v>
       </c>
       <c r="D84" s="1"/>
@@ -7029,7 +7030,7 @@
       <c r="B85" s="1">
         <v>3</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="2" t="s">
         <v>285</v>
       </c>
       <c r="D85" s="1"/>
@@ -7049,7 +7050,7 @@
       <c r="B86" s="1">
         <v>2</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="2" t="s">
         <v>288</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -7069,7 +7070,7 @@
       <c r="B87" s="1">
         <v>3</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="2" t="s">
         <v>291</v>
       </c>
       <c r="D87" s="1"/>
@@ -7091,7 +7092,7 @@
       <c r="B88" s="1">
         <v>3</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="2" t="s">
         <v>294</v>
       </c>
       <c r="D88" s="1"/>
@@ -7113,7 +7114,7 @@
       <c r="B89" s="1">
         <v>3</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="2" t="s">
         <v>297</v>
       </c>
       <c r="D89" s="1"/>
@@ -7133,7 +7134,7 @@
       <c r="B90" s="1">
         <v>2</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="2" t="s">
         <v>300</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -7153,7 +7154,7 @@
       <c r="B91" s="1">
         <v>3</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="2" t="s">
         <v>303</v>
       </c>
       <c r="D91" s="1"/>
@@ -7175,7 +7176,7 @@
       <c r="B92" s="1">
         <v>3</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="2" t="s">
         <v>306</v>
       </c>
       <c r="D92" s="1"/>
@@ -7197,7 +7198,7 @@
       <c r="B93" s="1">
         <v>3</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="D93" s="1"/>
@@ -7217,7 +7218,7 @@
       <c r="B94" s="1">
         <v>2</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="2" t="s">
         <v>312</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -7237,7 +7238,7 @@
       <c r="B95" s="1">
         <v>3</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="2" t="s">
         <v>315</v>
       </c>
       <c r="D95" s="1"/>
@@ -7259,7 +7260,7 @@
       <c r="B96" s="1">
         <v>3</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="2" t="s">
         <v>318</v>
       </c>
       <c r="D96" s="1"/>
@@ -7281,7 +7282,7 @@
       <c r="B97" s="1">
         <v>3</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D97" s="1"/>
@@ -7303,7 +7304,7 @@
       <c r="B98" s="1">
         <v>3</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="2" t="s">
         <v>324</v>
       </c>
       <c r="D98" s="1"/>
@@ -7325,7 +7326,7 @@
       <c r="B99" s="1">
         <v>3</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="2" t="s">
         <v>327</v>
       </c>
       <c r="D99" s="1"/>
@@ -7347,7 +7348,7 @@
       <c r="B100" s="1">
         <v>3</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="2" t="s">
         <v>330</v>
       </c>
       <c r="D100" s="1"/>
@@ -7369,7 +7370,7 @@
       <c r="B101" s="1">
         <v>3</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="2" t="s">
         <v>333</v>
       </c>
       <c r="D101" s="1"/>
@@ -7391,7 +7392,7 @@
       <c r="B102" s="1">
         <v>3</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="2" t="s">
         <v>336</v>
       </c>
       <c r="D102" s="1"/>
@@ -7411,7 +7412,7 @@
       <c r="B103" s="1">
         <v>2</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -7431,7 +7432,7 @@
       <c r="B104" s="1">
         <v>3</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="2" t="s">
         <v>342</v>
       </c>
       <c r="D104" s="1"/>
@@ -7453,7 +7454,7 @@
       <c r="B105" s="1">
         <v>3</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="2" t="s">
         <v>345</v>
       </c>
       <c r="D105" s="1"/>
@@ -7475,7 +7476,7 @@
       <c r="B106" s="1">
         <v>3</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" s="2" t="s">
         <v>348</v>
       </c>
       <c r="D106" s="1"/>
@@ -7497,7 +7498,7 @@
       <c r="B107" s="1">
         <v>3</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C107" s="2" t="s">
         <v>351</v>
       </c>
       <c r="D107" s="1"/>
@@ -7517,7 +7518,7 @@
       <c r="B108" s="1">
         <v>1</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="2" t="s">
         <v>354</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -7535,7 +7536,7 @@
       <c r="B109" s="1">
         <v>2</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" s="2" t="s">
         <v>357</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -7555,7 +7556,7 @@
       <c r="B110" s="1">
         <v>3</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="2" t="s">
         <v>360</v>
       </c>
       <c r="D110" s="1"/>
@@ -7577,7 +7578,7 @@
       <c r="B111" s="1">
         <v>3</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="2" t="s">
         <v>363</v>
       </c>
       <c r="D111" s="1"/>
@@ -7599,7 +7600,7 @@
       <c r="B112" s="1">
         <v>3</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="2" t="s">
         <v>366</v>
       </c>
       <c r="D112" s="1"/>
@@ -7621,7 +7622,7 @@
       <c r="B113" s="1">
         <v>3</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C113" s="2" t="s">
         <v>369</v>
       </c>
       <c r="D113" s="1"/>
@@ -7643,7 +7644,7 @@
       <c r="B114" s="1">
         <v>3</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="2" t="s">
         <v>372</v>
       </c>
       <c r="D114" s="1"/>
@@ -7665,7 +7666,7 @@
       <c r="B115" s="1">
         <v>3</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="2" t="s">
         <v>375</v>
       </c>
       <c r="D115" s="1"/>
@@ -7687,7 +7688,7 @@
       <c r="B116" s="1">
         <v>3</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="2" t="s">
         <v>378</v>
       </c>
       <c r="D116" s="1"/>
@@ -7709,7 +7710,7 @@
       <c r="B117" s="1">
         <v>3</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="2" t="s">
         <v>381</v>
       </c>
       <c r="D117" s="1"/>
@@ -7731,7 +7732,7 @@
       <c r="B118" s="1">
         <v>3</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="2" t="s">
         <v>384</v>
       </c>
       <c r="D118" s="1"/>
@@ -7753,7 +7754,7 @@
       <c r="B119" s="1">
         <v>3</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="2" t="s">
         <v>387</v>
       </c>
       <c r="D119" s="1"/>
@@ -7775,7 +7776,7 @@
       <c r="B120" s="1">
         <v>3</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="2" t="s">
         <v>390</v>
       </c>
       <c r="D120" s="1"/>
@@ -7797,7 +7798,7 @@
       <c r="B121" s="1">
         <v>3</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="2" t="s">
         <v>393</v>
       </c>
       <c r="D121" s="1"/>
@@ -7819,7 +7820,7 @@
       <c r="B122" s="1">
         <v>3</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="2" t="s">
         <v>396</v>
       </c>
       <c r="D122" s="1"/>
@@ -7841,7 +7842,7 @@
       <c r="B123" s="1">
         <v>3</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" s="2" t="s">
         <v>399</v>
       </c>
       <c r="D123" s="1"/>
@@ -7863,7 +7864,7 @@
       <c r="B124" s="1">
         <v>3</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="2" t="s">
         <v>402</v>
       </c>
       <c r="D124" s="1"/>
@@ -7885,7 +7886,7 @@
       <c r="B125" s="1">
         <v>3</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="2" t="s">
         <v>405</v>
       </c>
       <c r="D125" s="1"/>
@@ -7907,7 +7908,7 @@
       <c r="B126" s="1">
         <v>3</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D126" s="1"/>
@@ -7929,7 +7930,7 @@
       <c r="B127" s="1">
         <v>3</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="2" t="s">
         <v>411</v>
       </c>
       <c r="D127" s="1"/>
@@ -7951,7 +7952,7 @@
       <c r="B128" s="1">
         <v>3</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="2" t="s">
         <v>414</v>
       </c>
       <c r="D128" s="1"/>
@@ -7973,7 +7974,7 @@
       <c r="B129" s="1">
         <v>3</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="2" t="s">
         <v>417</v>
       </c>
       <c r="D129" s="1"/>
@@ -7995,7 +7996,7 @@
       <c r="B130" s="1">
         <v>3</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="2" t="s">
         <v>420</v>
       </c>
       <c r="D130" s="1"/>
@@ -8017,7 +8018,7 @@
       <c r="B131" s="1">
         <v>3</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" s="2" t="s">
         <v>423</v>
       </c>
       <c r="D131" s="1"/>
@@ -8039,7 +8040,7 @@
       <c r="B132" s="1">
         <v>3</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" s="2" t="s">
         <v>426</v>
       </c>
       <c r="D132" s="1"/>
@@ -8061,7 +8062,7 @@
       <c r="B133" s="1">
         <v>3</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C133" s="2" t="s">
         <v>429</v>
       </c>
       <c r="D133" s="1"/>
@@ -8083,7 +8084,7 @@
       <c r="B134" s="1">
         <v>3</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C134" s="2" t="s">
         <v>432</v>
       </c>
       <c r="D134" s="1"/>
@@ -8105,7 +8106,7 @@
       <c r="B135" s="1">
         <v>3</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="C135" s="2" t="s">
         <v>435</v>
       </c>
       <c r="D135" s="1"/>
@@ -8127,7 +8128,7 @@
       <c r="B136" s="1">
         <v>3</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C136" s="2" t="s">
         <v>438</v>
       </c>
       <c r="D136" s="1"/>
@@ -8149,7 +8150,7 @@
       <c r="B137" s="1">
         <v>3</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C137" s="2" t="s">
         <v>441</v>
       </c>
       <c r="D137" s="1"/>
@@ -8171,7 +8172,7 @@
       <c r="B138" s="1">
         <v>3</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C138" s="2" t="s">
         <v>444</v>
       </c>
       <c r="D138" s="1"/>
@@ -8193,7 +8194,7 @@
       <c r="B139" s="1">
         <v>3</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C139" s="2" t="s">
         <v>447</v>
       </c>
       <c r="D139" s="1"/>
@@ -8215,7 +8216,7 @@
       <c r="B140" s="1">
         <v>3</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C140" s="2" t="s">
         <v>450</v>
       </c>
       <c r="D140" s="1"/>
@@ -8237,7 +8238,7 @@
       <c r="B141" s="1">
         <v>3</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="C141" s="2" t="s">
         <v>453</v>
       </c>
       <c r="D141" s="1"/>
@@ -8259,7 +8260,7 @@
       <c r="B142" s="1">
         <v>3</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" s="2" t="s">
         <v>456</v>
       </c>
       <c r="D142" s="1"/>
@@ -8279,7 +8280,7 @@
       <c r="B143" s="1">
         <v>2</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="C143" s="2" t="s">
         <v>459</v>
       </c>
       <c r="D143" s="1" t="s">
@@ -8299,7 +8300,7 @@
       <c r="B144" s="1">
         <v>3</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C144" s="2" t="s">
         <v>462</v>
       </c>
       <c r="D144" s="1"/>
@@ -8321,7 +8322,7 @@
       <c r="B145" s="1">
         <v>3</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C145" s="2" t="s">
         <v>465</v>
       </c>
       <c r="D145" s="1"/>
@@ -8343,7 +8344,7 @@
       <c r="B146" s="1">
         <v>3</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="C146" s="2" t="s">
         <v>468</v>
       </c>
       <c r="D146" s="1"/>
@@ -8365,7 +8366,7 @@
       <c r="B147" s="1">
         <v>3</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="C147" s="2" t="s">
         <v>471</v>
       </c>
       <c r="D147" s="1"/>
@@ -8387,7 +8388,7 @@
       <c r="B148" s="1">
         <v>3</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="C148" s="2" t="s">
         <v>474</v>
       </c>
       <c r="D148" s="1"/>
@@ -8409,7 +8410,7 @@
       <c r="B149" s="1">
         <v>3</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="C149" s="2" t="s">
         <v>477</v>
       </c>
       <c r="D149" s="1"/>
@@ -8431,7 +8432,7 @@
       <c r="B150" s="1">
         <v>3</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="C150" s="2" t="s">
         <v>480</v>
       </c>
       <c r="D150" s="1"/>
@@ -8453,7 +8454,7 @@
       <c r="B151" s="1">
         <v>3</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="C151" s="2" t="s">
         <v>483</v>
       </c>
       <c r="D151" s="1"/>
@@ -8475,7 +8476,7 @@
       <c r="B152" s="1">
         <v>3</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="C152" s="2" t="s">
         <v>486</v>
       </c>
       <c r="D152" s="1"/>
@@ -8497,7 +8498,7 @@
       <c r="B153" s="1">
         <v>3</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="C153" s="2" t="s">
         <v>489</v>
       </c>
       <c r="D153" s="1"/>
@@ -8519,7 +8520,7 @@
       <c r="B154" s="1">
         <v>3</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C154" s="2" t="s">
         <v>492</v>
       </c>
       <c r="D154" s="1"/>
@@ -8541,7 +8542,7 @@
       <c r="B155" s="1">
         <v>3</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="C155" s="2" t="s">
         <v>495</v>
       </c>
       <c r="D155" s="1"/>
@@ -8563,7 +8564,7 @@
       <c r="B156" s="1">
         <v>3</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C156" s="2" t="s">
         <v>498</v>
       </c>
       <c r="D156" s="1"/>
@@ -8585,7 +8586,7 @@
       <c r="B157" s="1">
         <v>3</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="C157" s="2" t="s">
         <v>501</v>
       </c>
       <c r="D157" s="1"/>
@@ -8605,7 +8606,7 @@
       <c r="B158" s="1">
         <v>2</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="C158" s="2" t="s">
         <v>504</v>
       </c>
       <c r="D158" s="1" t="s">
@@ -8625,7 +8626,7 @@
       <c r="B159" s="1">
         <v>3</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="C159" s="2" t="s">
         <v>507</v>
       </c>
       <c r="D159" s="1"/>
@@ -8647,7 +8648,7 @@
       <c r="B160" s="1">
         <v>3</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="C160" s="2" t="s">
         <v>510</v>
       </c>
       <c r="D160" s="1"/>
@@ -8669,7 +8670,7 @@
       <c r="B161" s="1">
         <v>3</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="C161" s="2" t="s">
         <v>513</v>
       </c>
       <c r="D161" s="1"/>
@@ -8691,7 +8692,7 @@
       <c r="B162" s="1">
         <v>3</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="C162" s="2" t="s">
         <v>516</v>
       </c>
       <c r="D162" s="1"/>
@@ -8713,7 +8714,7 @@
       <c r="B163" s="1">
         <v>3</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="C163" s="2" t="s">
         <v>519</v>
       </c>
       <c r="D163" s="1"/>
@@ -8735,7 +8736,7 @@
       <c r="B164" s="1">
         <v>3</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="C164" s="2" t="s">
         <v>522</v>
       </c>
       <c r="D164" s="1"/>
@@ -8757,7 +8758,7 @@
       <c r="B165" s="1">
         <v>3</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="C165" s="2" t="s">
         <v>525</v>
       </c>
       <c r="D165" s="1"/>
@@ -8779,7 +8780,7 @@
       <c r="B166" s="1">
         <v>3</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="C166" s="2" t="s">
         <v>528</v>
       </c>
       <c r="D166" s="1"/>
@@ -8801,7 +8802,7 @@
       <c r="B167" s="1">
         <v>3</v>
       </c>
-      <c r="C167" s="1" t="s">
+      <c r="C167" s="2" t="s">
         <v>531</v>
       </c>
       <c r="D167" s="1"/>
@@ -8823,7 +8824,7 @@
       <c r="B168" s="1">
         <v>3</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="C168" s="2" t="s">
         <v>534</v>
       </c>
       <c r="D168" s="1"/>
@@ -8845,7 +8846,7 @@
       <c r="B169" s="1">
         <v>3</v>
       </c>
-      <c r="C169" s="1" t="s">
+      <c r="C169" s="2" t="s">
         <v>537</v>
       </c>
       <c r="D169" s="1"/>
@@ -8867,7 +8868,7 @@
       <c r="B170" s="1">
         <v>3</v>
       </c>
-      <c r="C170" s="1" t="s">
+      <c r="C170" s="2" t="s">
         <v>540</v>
       </c>
       <c r="D170" s="1"/>
@@ -8889,7 +8890,7 @@
       <c r="B171" s="1">
         <v>3</v>
       </c>
-      <c r="C171" s="1" t="s">
+      <c r="C171" s="2" t="s">
         <v>543</v>
       </c>
       <c r="D171" s="1"/>
@@ -8911,7 +8912,7 @@
       <c r="B172" s="1">
         <v>3</v>
       </c>
-      <c r="C172" s="1" t="s">
+      <c r="C172" s="2" t="s">
         <v>546</v>
       </c>
       <c r="D172" s="1"/>
@@ -8933,7 +8934,7 @@
       <c r="B173" s="1">
         <v>3</v>
       </c>
-      <c r="C173" s="1" t="s">
+      <c r="C173" s="2" t="s">
         <v>549</v>
       </c>
       <c r="D173" s="1"/>
@@ -8955,7 +8956,7 @@
       <c r="B174" s="1">
         <v>3</v>
       </c>
-      <c r="C174" s="1" t="s">
+      <c r="C174" s="2" t="s">
         <v>552</v>
       </c>
       <c r="D174" s="1"/>
@@ -8977,7 +8978,7 @@
       <c r="B175" s="1">
         <v>3</v>
       </c>
-      <c r="C175" s="1" t="s">
+      <c r="C175" s="2" t="s">
         <v>555</v>
       </c>
       <c r="D175" s="1"/>
@@ -8999,7 +9000,7 @@
       <c r="B176" s="1">
         <v>3</v>
       </c>
-      <c r="C176" s="1" t="s">
+      <c r="C176" s="2" t="s">
         <v>558</v>
       </c>
       <c r="D176" s="1"/>
@@ -9021,7 +9022,7 @@
       <c r="B177" s="1">
         <v>3</v>
       </c>
-      <c r="C177" s="1" t="s">
+      <c r="C177" s="2" t="s">
         <v>561</v>
       </c>
       <c r="D177" s="1"/>
@@ -9043,7 +9044,7 @@
       <c r="B178" s="1">
         <v>3</v>
       </c>
-      <c r="C178" s="1" t="s">
+      <c r="C178" s="2" t="s">
         <v>564</v>
       </c>
       <c r="D178" s="1"/>
@@ -9065,7 +9066,7 @@
       <c r="B179" s="1">
         <v>3</v>
       </c>
-      <c r="C179" s="1" t="s">
+      <c r="C179" s="2" t="s">
         <v>567</v>
       </c>
       <c r="D179" s="1"/>
@@ -9087,7 +9088,7 @@
       <c r="B180" s="1">
         <v>3</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="C180" s="2" t="s">
         <v>570</v>
       </c>
       <c r="D180" s="1"/>
@@ -9109,7 +9110,7 @@
       <c r="B181" s="1">
         <v>3</v>
       </c>
-      <c r="C181" s="1" t="s">
+      <c r="C181" s="2" t="s">
         <v>573</v>
       </c>
       <c r="D181" s="1"/>
@@ -9131,7 +9132,7 @@
       <c r="B182" s="1">
         <v>3</v>
       </c>
-      <c r="C182" s="1" t="s">
+      <c r="C182" s="2" t="s">
         <v>577</v>
       </c>
       <c r="D182" s="1"/>
@@ -9153,7 +9154,7 @@
       <c r="B183" s="1">
         <v>3</v>
       </c>
-      <c r="C183" s="1" t="s">
+      <c r="C183" s="2" t="s">
         <v>580</v>
       </c>
       <c r="D183" s="1"/>
@@ -9175,7 +9176,7 @@
       <c r="B184" s="1">
         <v>3</v>
       </c>
-      <c r="C184" s="1" t="s">
+      <c r="C184" s="2" t="s">
         <v>583</v>
       </c>
       <c r="D184" s="1"/>
@@ -9197,7 +9198,7 @@
       <c r="B185" s="1">
         <v>3</v>
       </c>
-      <c r="C185" s="1" t="s">
+      <c r="C185" s="2" t="s">
         <v>586</v>
       </c>
       <c r="D185" s="1"/>
@@ -9219,7 +9220,7 @@
       <c r="B186" s="1">
         <v>3</v>
       </c>
-      <c r="C186" s="1" t="s">
+      <c r="C186" s="2" t="s">
         <v>589</v>
       </c>
       <c r="D186" s="1"/>
@@ -9241,7 +9242,7 @@
       <c r="B187" s="1">
         <v>3</v>
       </c>
-      <c r="C187" s="1" t="s">
+      <c r="C187" s="2" t="s">
         <v>592</v>
       </c>
       <c r="D187" s="1"/>
@@ -9263,7 +9264,7 @@
       <c r="B188" s="1">
         <v>3</v>
       </c>
-      <c r="C188" s="1" t="s">
+      <c r="C188" s="2" t="s">
         <v>595</v>
       </c>
       <c r="D188" s="1"/>
@@ -9285,7 +9286,7 @@
       <c r="B189" s="1">
         <v>3</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="C189" s="2" t="s">
         <v>598</v>
       </c>
       <c r="D189" s="1"/>
@@ -9307,7 +9308,7 @@
       <c r="B190" s="1">
         <v>3</v>
       </c>
-      <c r="C190" s="1" t="s">
+      <c r="C190" s="2" t="s">
         <v>601</v>
       </c>
       <c r="D190" s="1"/>
@@ -9329,7 +9330,7 @@
       <c r="B191" s="1">
         <v>3</v>
       </c>
-      <c r="C191" s="1" t="s">
+      <c r="C191" s="2" t="s">
         <v>604</v>
       </c>
       <c r="D191" s="1"/>
@@ -9349,7 +9350,7 @@
       <c r="B192" s="1">
         <v>2</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="C192" s="2" t="s">
         <v>607</v>
       </c>
       <c r="D192" s="1" t="s">
@@ -9369,7 +9370,7 @@
       <c r="B193" s="1">
         <v>3</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="C193" s="2" t="s">
         <v>610</v>
       </c>
       <c r="D193" s="1"/>
@@ -9391,7 +9392,7 @@
       <c r="B194" s="1">
         <v>3</v>
       </c>
-      <c r="C194" s="1" t="s">
+      <c r="C194" s="2" t="s">
         <v>613</v>
       </c>
       <c r="D194" s="1"/>
@@ -9413,7 +9414,7 @@
       <c r="B195" s="1">
         <v>3</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="C195" s="2" t="s">
         <v>616</v>
       </c>
       <c r="D195" s="1"/>
@@ -9435,7 +9436,7 @@
       <c r="B196" s="1">
         <v>3</v>
       </c>
-      <c r="C196" s="1" t="s">
+      <c r="C196" s="2" t="s">
         <v>619</v>
       </c>
       <c r="D196" s="1"/>
@@ -9457,7 +9458,7 @@
       <c r="B197" s="1">
         <v>3</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="C197" s="2" t="s">
         <v>622</v>
       </c>
       <c r="D197" s="1"/>
@@ -9479,7 +9480,7 @@
       <c r="B198" s="1">
         <v>3</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="C198" s="2" t="s">
         <v>625</v>
       </c>
       <c r="D198" s="1"/>
@@ -9501,7 +9502,7 @@
       <c r="B199" s="1">
         <v>3</v>
       </c>
-      <c r="C199" s="1" t="s">
+      <c r="C199" s="2" t="s">
         <v>628</v>
       </c>
       <c r="D199" s="1"/>
@@ -9523,7 +9524,7 @@
       <c r="B200" s="1">
         <v>3</v>
       </c>
-      <c r="C200" s="1" t="s">
+      <c r="C200" s="2" t="s">
         <v>631</v>
       </c>
       <c r="D200" s="1"/>
@@ -9543,7 +9544,7 @@
       <c r="B201" s="1">
         <v>2</v>
       </c>
-      <c r="C201" s="1" t="s">
+      <c r="C201" s="2" t="s">
         <v>634</v>
       </c>
       <c r="D201" s="1" t="s">
@@ -9563,7 +9564,7 @@
       <c r="B202" s="1">
         <v>3</v>
       </c>
-      <c r="C202" s="1" t="s">
+      <c r="C202" s="2" t="s">
         <v>637</v>
       </c>
       <c r="D202" s="1"/>
@@ -9585,7 +9586,7 @@
       <c r="B203" s="1">
         <v>3</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="C203" s="2" t="s">
         <v>640</v>
       </c>
       <c r="D203" s="1"/>
@@ -9607,7 +9608,7 @@
       <c r="B204" s="1">
         <v>3</v>
       </c>
-      <c r="C204" s="1" t="s">
+      <c r="C204" s="2" t="s">
         <v>643</v>
       </c>
       <c r="D204" s="1"/>
@@ -9629,7 +9630,7 @@
       <c r="B205" s="1">
         <v>3</v>
       </c>
-      <c r="C205" s="1" t="s">
+      <c r="C205" s="2" t="s">
         <v>646</v>
       </c>
       <c r="D205" s="1"/>
@@ -9649,7 +9650,7 @@
       <c r="B206" s="1">
         <v>2</v>
       </c>
-      <c r="C206" s="1" t="s">
+      <c r="C206" s="2" t="s">
         <v>649</v>
       </c>
       <c r="D206" s="1" t="s">
@@ -9669,7 +9670,7 @@
       <c r="B207" s="1">
         <v>3</v>
       </c>
-      <c r="C207" s="1" t="s">
+      <c r="C207" s="2" t="s">
         <v>652</v>
       </c>
       <c r="D207" s="1"/>
@@ -9691,7 +9692,7 @@
       <c r="B208" s="1">
         <v>3</v>
       </c>
-      <c r="C208" s="1" t="s">
+      <c r="C208" s="2" t="s">
         <v>655</v>
       </c>
       <c r="D208" s="1"/>
@@ -9713,7 +9714,7 @@
       <c r="B209" s="1">
         <v>3</v>
       </c>
-      <c r="C209" s="1" t="s">
+      <c r="C209" s="2" t="s">
         <v>658</v>
       </c>
       <c r="D209" s="1"/>
@@ -9733,7 +9734,7 @@
       <c r="B210" s="1">
         <v>2</v>
       </c>
-      <c r="C210" s="1" t="s">
+      <c r="C210" s="2" t="s">
         <v>661</v>
       </c>
       <c r="D210" s="1" t="s">
@@ -9753,7 +9754,7 @@
       <c r="B211" s="1">
         <v>3</v>
       </c>
-      <c r="C211" s="1" t="s">
+      <c r="C211" s="2" t="s">
         <v>664</v>
       </c>
       <c r="D211" s="1"/>
@@ -9773,7 +9774,7 @@
       <c r="B212" s="1">
         <v>2</v>
       </c>
-      <c r="C212" s="1" t="s">
+      <c r="C212" s="2" t="s">
         <v>667</v>
       </c>
       <c r="D212" s="1" t="s">
@@ -9793,7 +9794,7 @@
       <c r="B213" s="1">
         <v>3</v>
       </c>
-      <c r="C213" s="1" t="s">
+      <c r="C213" s="2" t="s">
         <v>670</v>
       </c>
       <c r="D213" s="1"/>
@@ -9815,7 +9816,7 @@
       <c r="B214" s="1">
         <v>3</v>
       </c>
-      <c r="C214" s="1" t="s">
+      <c r="C214" s="2" t="s">
         <v>673</v>
       </c>
       <c r="D214" s="1"/>
@@ -9837,7 +9838,7 @@
       <c r="B215" s="1">
         <v>3</v>
       </c>
-      <c r="C215" s="1" t="s">
+      <c r="C215" s="2" t="s">
         <v>676</v>
       </c>
       <c r="D215" s="1"/>
@@ -9859,7 +9860,7 @@
       <c r="B216" s="1">
         <v>3</v>
       </c>
-      <c r="C216" s="1" t="s">
+      <c r="C216" s="2" t="s">
         <v>679</v>
       </c>
       <c r="D216" s="1"/>
@@ -9881,7 +9882,7 @@
       <c r="B217" s="1">
         <v>3</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="C217" s="2" t="s">
         <v>682</v>
       </c>
       <c r="D217" s="1"/>
@@ -9903,7 +9904,7 @@
       <c r="B218" s="1">
         <v>3</v>
       </c>
-      <c r="C218" s="1" t="s">
+      <c r="C218" s="2" t="s">
         <v>685</v>
       </c>
       <c r="D218" s="1"/>
@@ -9925,7 +9926,7 @@
       <c r="B219" s="1">
         <v>3</v>
       </c>
-      <c r="C219" s="1" t="s">
+      <c r="C219" s="2" t="s">
         <v>688</v>
       </c>
       <c r="D219" s="1"/>
@@ -9947,7 +9948,7 @@
       <c r="B220" s="1">
         <v>3</v>
       </c>
-      <c r="C220" s="1" t="s">
+      <c r="C220" s="2" t="s">
         <v>689</v>
       </c>
       <c r="D220" s="1"/>
@@ -9969,7 +9970,7 @@
       <c r="B221" s="1">
         <v>3</v>
       </c>
-      <c r="C221" s="1" t="s">
+      <c r="C221" s="2" t="s">
         <v>690</v>
       </c>
       <c r="D221" s="1"/>
@@ -9989,7 +9990,7 @@
       <c r="B222" s="1">
         <v>2</v>
       </c>
-      <c r="C222" s="1" t="s">
+      <c r="C222" s="2" t="s">
         <v>693</v>
       </c>
       <c r="D222" s="1" t="s">
@@ -10009,7 +10010,7 @@
       <c r="B223" s="1">
         <v>3</v>
       </c>
-      <c r="C223" s="1" t="s">
+      <c r="C223" s="2" t="s">
         <v>696</v>
       </c>
       <c r="D223" s="1"/>
@@ -10031,7 +10032,7 @@
       <c r="B224" s="1">
         <v>3</v>
       </c>
-      <c r="C224" s="1" t="s">
+      <c r="C224" s="2" t="s">
         <v>699</v>
       </c>
       <c r="D224" s="1"/>
@@ -10053,7 +10054,7 @@
       <c r="B225" s="1">
         <v>3</v>
       </c>
-      <c r="C225" s="1" t="s">
+      <c r="C225" s="2" t="s">
         <v>702</v>
       </c>
       <c r="D225" s="1"/>
@@ -10075,7 +10076,7 @@
       <c r="B226" s="1">
         <v>3</v>
       </c>
-      <c r="C226" s="1" t="s">
+      <c r="C226" s="2" t="s">
         <v>705</v>
       </c>
       <c r="D226" s="1"/>
@@ -10097,7 +10098,7 @@
       <c r="B227" s="1">
         <v>3</v>
       </c>
-      <c r="C227" s="1" t="s">
+      <c r="C227" s="2" t="s">
         <v>708</v>
       </c>
       <c r="D227" s="1"/>
@@ -10119,7 +10120,7 @@
       <c r="B228" s="1">
         <v>3</v>
       </c>
-      <c r="C228" s="1" t="s">
+      <c r="C228" s="2" t="s">
         <v>711</v>
       </c>
       <c r="D228" s="1"/>
@@ -10141,7 +10142,7 @@
       <c r="B229" s="1">
         <v>3</v>
       </c>
-      <c r="C229" s="1" t="s">
+      <c r="C229" s="2" t="s">
         <v>714</v>
       </c>
       <c r="D229" s="1"/>
@@ -10163,7 +10164,7 @@
       <c r="B230" s="1">
         <v>3</v>
       </c>
-      <c r="C230" s="1" t="s">
+      <c r="C230" s="2" t="s">
         <v>717</v>
       </c>
       <c r="D230" s="1"/>
@@ -10185,7 +10186,7 @@
       <c r="B231" s="1">
         <v>3</v>
       </c>
-      <c r="C231" s="1" t="s">
+      <c r="C231" s="2" t="s">
         <v>720</v>
       </c>
       <c r="D231" s="1"/>
@@ -10207,7 +10208,7 @@
       <c r="B232" s="1">
         <v>3</v>
       </c>
-      <c r="C232" s="1" t="s">
+      <c r="C232" s="2" t="s">
         <v>723</v>
       </c>
       <c r="D232" s="1"/>
@@ -10229,7 +10230,7 @@
       <c r="B233" s="1">
         <v>3</v>
       </c>
-      <c r="C233" s="1" t="s">
+      <c r="C233" s="2" t="s">
         <v>726</v>
       </c>
       <c r="D233" s="1"/>
@@ -10251,7 +10252,7 @@
       <c r="B234" s="1">
         <v>3</v>
       </c>
-      <c r="C234" s="1" t="s">
+      <c r="C234" s="2" t="s">
         <v>729</v>
       </c>
       <c r="D234" s="1"/>
@@ -10271,7 +10272,7 @@
       <c r="B235" s="1">
         <v>1</v>
       </c>
-      <c r="C235" s="1" t="s">
+      <c r="C235" s="2" t="s">
         <v>256</v>
       </c>
       <c r="D235" s="1" t="s">
@@ -10289,7 +10290,7 @@
       <c r="B236" s="1">
         <v>2</v>
       </c>
-      <c r="C236" s="1" t="s">
+      <c r="C236" s="2" t="s">
         <v>734</v>
       </c>
       <c r="D236" s="1" t="s">
@@ -10309,7 +10310,7 @@
       <c r="B237" s="1">
         <v>3</v>
       </c>
-      <c r="C237" s="1" t="s">
+      <c r="C237" s="2" t="s">
         <v>737</v>
       </c>
       <c r="D237" s="1"/>
@@ -10331,7 +10332,7 @@
       <c r="B238" s="1">
         <v>3</v>
       </c>
-      <c r="C238" s="1" t="s">
+      <c r="C238" s="2" t="s">
         <v>740</v>
       </c>
       <c r="D238" s="1"/>
@@ -10353,7 +10354,7 @@
       <c r="B239" s="1">
         <v>3</v>
       </c>
-      <c r="C239" s="1" t="s">
+      <c r="C239" s="2" t="s">
         <v>743</v>
       </c>
       <c r="D239" s="1"/>
@@ -10375,7 +10376,7 @@
       <c r="B240" s="1">
         <v>3</v>
       </c>
-      <c r="C240" s="1" t="s">
+      <c r="C240" s="2" t="s">
         <v>746</v>
       </c>
       <c r="D240" s="1"/>
@@ -10397,7 +10398,7 @@
       <c r="B241" s="1">
         <v>3</v>
       </c>
-      <c r="C241" s="1" t="s">
+      <c r="C241" s="2" t="s">
         <v>749</v>
       </c>
       <c r="D241" s="1"/>
@@ -10419,7 +10420,7 @@
       <c r="B242" s="1">
         <v>3</v>
       </c>
-      <c r="C242" s="1" t="s">
+      <c r="C242" s="2" t="s">
         <v>752</v>
       </c>
       <c r="D242" s="1"/>
@@ -10441,7 +10442,7 @@
       <c r="B243" s="1">
         <v>3</v>
       </c>
-      <c r="C243" s="1" t="s">
+      <c r="C243" s="2" t="s">
         <v>754</v>
       </c>
       <c r="D243" s="1"/>
@@ -10463,7 +10464,7 @@
       <c r="B244" s="1">
         <v>3</v>
       </c>
-      <c r="C244" s="1" t="s">
+      <c r="C244" s="2" t="s">
         <v>757</v>
       </c>
       <c r="D244" s="1"/>
@@ -10485,7 +10486,7 @@
       <c r="B245" s="1">
         <v>3</v>
       </c>
-      <c r="C245" s="1" t="s">
+      <c r="C245" s="2" t="s">
         <v>760</v>
       </c>
       <c r="D245" s="1"/>
@@ -10507,7 +10508,7 @@
       <c r="B246" s="1">
         <v>3</v>
       </c>
-      <c r="C246" s="1" t="s">
+      <c r="C246" s="2" t="s">
         <v>763</v>
       </c>
       <c r="D246" s="1"/>
@@ -10529,7 +10530,7 @@
       <c r="B247" s="1">
         <v>3</v>
       </c>
-      <c r="C247" s="1" t="s">
+      <c r="C247" s="2" t="s">
         <v>766</v>
       </c>
       <c r="D247" s="1"/>
@@ -10549,7 +10550,7 @@
       <c r="B248" s="1">
         <v>2</v>
       </c>
-      <c r="C248" s="1" t="s">
+      <c r="C248" s="2" t="s">
         <v>769</v>
       </c>
       <c r="D248" s="1" t="s">
@@ -10569,7 +10570,7 @@
       <c r="B249" s="1">
         <v>3</v>
       </c>
-      <c r="C249" s="1" t="s">
+      <c r="C249" s="2" t="s">
         <v>772</v>
       </c>
       <c r="D249" s="1"/>
@@ -10591,7 +10592,7 @@
       <c r="B250" s="1">
         <v>3</v>
       </c>
-      <c r="C250" s="1" t="s">
+      <c r="C250" s="2" t="s">
         <v>775</v>
       </c>
       <c r="D250" s="1"/>
@@ -10613,7 +10614,7 @@
       <c r="B251" s="1">
         <v>3</v>
       </c>
-      <c r="C251" s="1" t="s">
+      <c r="C251" s="2" t="s">
         <v>778</v>
       </c>
       <c r="D251" s="1"/>
@@ -10635,7 +10636,7 @@
       <c r="B252" s="1">
         <v>3</v>
       </c>
-      <c r="C252" s="1" t="s">
+      <c r="C252" s="2" t="s">
         <v>781</v>
       </c>
       <c r="D252" s="1"/>
@@ -10657,7 +10658,7 @@
       <c r="B253" s="1">
         <v>3</v>
       </c>
-      <c r="C253" s="1" t="s">
+      <c r="C253" s="2" t="s">
         <v>784</v>
       </c>
       <c r="D253" s="1"/>
@@ -10679,7 +10680,7 @@
       <c r="B254" s="1">
         <v>3</v>
       </c>
-      <c r="C254" s="1" t="s">
+      <c r="C254" s="2" t="s">
         <v>787</v>
       </c>
       <c r="D254" s="1"/>
@@ -10701,7 +10702,7 @@
       <c r="B255" s="1">
         <v>3</v>
       </c>
-      <c r="C255" s="1" t="s">
+      <c r="C255" s="2" t="s">
         <v>790</v>
       </c>
       <c r="D255" s="1"/>
@@ -10723,7 +10724,7 @@
       <c r="B256" s="1">
         <v>3</v>
       </c>
-      <c r="C256" s="1" t="s">
+      <c r="C256" s="2" t="s">
         <v>793</v>
       </c>
       <c r="D256" s="1"/>
@@ -10745,7 +10746,7 @@
       <c r="B257" s="1">
         <v>3</v>
       </c>
-      <c r="C257" s="1" t="s">
+      <c r="C257" s="2" t="s">
         <v>796</v>
       </c>
       <c r="D257" s="1"/>
@@ -10767,7 +10768,7 @@
       <c r="B258" s="1">
         <v>3</v>
       </c>
-      <c r="C258" s="1" t="s">
+      <c r="C258" s="2" t="s">
         <v>799</v>
       </c>
       <c r="D258" s="1"/>
@@ -10789,7 +10790,7 @@
       <c r="B259" s="1">
         <v>3</v>
       </c>
-      <c r="C259" s="1" t="s">
+      <c r="C259" s="2" t="s">
         <v>802</v>
       </c>
       <c r="D259" s="1"/>
@@ -10809,7 +10810,7 @@
       <c r="B260" s="1">
         <v>2</v>
       </c>
-      <c r="C260" s="1" t="s">
+      <c r="C260" s="2" t="s">
         <v>805</v>
       </c>
       <c r="D260" s="1" t="s">
@@ -10829,7 +10830,7 @@
       <c r="B261" s="1">
         <v>3</v>
       </c>
-      <c r="C261" s="1" t="s">
+      <c r="C261" s="2" t="s">
         <v>808</v>
       </c>
       <c r="D261" s="1"/>
@@ -10851,7 +10852,7 @@
       <c r="B262" s="1">
         <v>3</v>
       </c>
-      <c r="C262" s="1" t="s">
+      <c r="C262" s="2" t="s">
         <v>811</v>
       </c>
       <c r="D262" s="1"/>
@@ -10873,7 +10874,7 @@
       <c r="B263" s="1">
         <v>3</v>
       </c>
-      <c r="C263" s="1" t="s">
+      <c r="C263" s="2" t="s">
         <v>814</v>
       </c>
       <c r="D263" s="1"/>
@@ -10895,7 +10896,7 @@
       <c r="B264" s="1">
         <v>3</v>
       </c>
-      <c r="C264" s="1" t="s">
+      <c r="C264" s="2" t="s">
         <v>817</v>
       </c>
       <c r="D264" s="1"/>
@@ -10917,7 +10918,7 @@
       <c r="B265" s="1">
         <v>3</v>
       </c>
-      <c r="C265" s="1" t="s">
+      <c r="C265" s="2" t="s">
         <v>820</v>
       </c>
       <c r="D265" s="1"/>
@@ -10939,7 +10940,7 @@
       <c r="B266" s="1">
         <v>3</v>
       </c>
-      <c r="C266" s="1" t="s">
+      <c r="C266" s="2" t="s">
         <v>823</v>
       </c>
       <c r="D266" s="1"/>
@@ -10961,7 +10962,7 @@
       <c r="B267" s="1">
         <v>3</v>
       </c>
-      <c r="C267" s="1" t="s">
+      <c r="C267" s="2" t="s">
         <v>826</v>
       </c>
       <c r="D267" s="1"/>
@@ -10983,7 +10984,7 @@
       <c r="B268" s="1">
         <v>3</v>
       </c>
-      <c r="C268" s="1" t="s">
+      <c r="C268" s="2" t="s">
         <v>829</v>
       </c>
       <c r="D268" s="1"/>
@@ -11005,7 +11006,7 @@
       <c r="B269" s="1">
         <v>3</v>
       </c>
-      <c r="C269" s="1" t="s">
+      <c r="C269" s="2" t="s">
         <v>832</v>
       </c>
       <c r="D269" s="1"/>
@@ -11027,7 +11028,7 @@
       <c r="B270" s="1">
         <v>3</v>
       </c>
-      <c r="C270" s="1" t="s">
+      <c r="C270" s="2" t="s">
         <v>835</v>
       </c>
       <c r="D270" s="1"/>
@@ -11049,7 +11050,7 @@
       <c r="B271" s="1">
         <v>3</v>
       </c>
-      <c r="C271" s="1" t="s">
+      <c r="C271" s="2" t="s">
         <v>838</v>
       </c>
       <c r="D271" s="1"/>
@@ -11071,7 +11072,7 @@
       <c r="B272" s="1">
         <v>3</v>
       </c>
-      <c r="C272" s="1" t="s">
+      <c r="C272" s="2" t="s">
         <v>841</v>
       </c>
       <c r="D272" s="1"/>
@@ -11093,7 +11094,7 @@
       <c r="B273" s="1">
         <v>3</v>
       </c>
-      <c r="C273" s="1" t="s">
+      <c r="C273" s="2" t="s">
         <v>844</v>
       </c>
       <c r="D273" s="1"/>
@@ -11115,7 +11116,7 @@
       <c r="B274" s="1">
         <v>3</v>
       </c>
-      <c r="C274" s="1" t="s">
+      <c r="C274" s="2" t="s">
         <v>847</v>
       </c>
       <c r="D274" s="1"/>
@@ -11137,7 +11138,7 @@
       <c r="B275" s="1">
         <v>3</v>
       </c>
-      <c r="C275" s="1" t="s">
+      <c r="C275" s="2" t="s">
         <v>850</v>
       </c>
       <c r="D275" s="1"/>
@@ -11159,7 +11160,7 @@
       <c r="B276" s="1">
         <v>3</v>
       </c>
-      <c r="C276" s="1" t="s">
+      <c r="C276" s="2" t="s">
         <v>853</v>
       </c>
       <c r="D276" s="1"/>
@@ -11181,7 +11182,7 @@
       <c r="B277" s="1">
         <v>3</v>
       </c>
-      <c r="C277" s="1" t="s">
+      <c r="C277" s="2" t="s">
         <v>856</v>
       </c>
       <c r="D277" s="1"/>
@@ -11203,7 +11204,7 @@
       <c r="B278" s="1">
         <v>3</v>
       </c>
-      <c r="C278" s="1" t="s">
+      <c r="C278" s="2" t="s">
         <v>859</v>
       </c>
       <c r="D278" s="1"/>
@@ -11225,7 +11226,7 @@
       <c r="B279" s="1">
         <v>3</v>
       </c>
-      <c r="C279" s="1" t="s">
+      <c r="C279" s="2" t="s">
         <v>862</v>
       </c>
       <c r="D279" s="1"/>
@@ -11247,7 +11248,7 @@
       <c r="B280" s="1">
         <v>3</v>
       </c>
-      <c r="C280" s="1" t="s">
+      <c r="C280" s="2" t="s">
         <v>865</v>
       </c>
       <c r="D280" s="1"/>
@@ -11269,7 +11270,7 @@
       <c r="B281" s="1">
         <v>3</v>
       </c>
-      <c r="C281" s="1" t="s">
+      <c r="C281" s="2" t="s">
         <v>868</v>
       </c>
       <c r="D281" s="1"/>
@@ -11291,7 +11292,7 @@
       <c r="B282" s="1">
         <v>3</v>
       </c>
-      <c r="C282" s="1" t="s">
+      <c r="C282" s="2" t="s">
         <v>871</v>
       </c>
       <c r="D282" s="1"/>
@@ -11313,7 +11314,7 @@
       <c r="B283" s="1">
         <v>3</v>
       </c>
-      <c r="C283" s="1" t="s">
+      <c r="C283" s="2" t="s">
         <v>874</v>
       </c>
       <c r="D283" s="1"/>
@@ -11335,7 +11336,7 @@
       <c r="B284" s="1">
         <v>3</v>
       </c>
-      <c r="C284" s="1" t="s">
+      <c r="C284" s="2" t="s">
         <v>877</v>
       </c>
       <c r="D284" s="1"/>
@@ -11357,7 +11358,7 @@
       <c r="B285" s="1">
         <v>3</v>
       </c>
-      <c r="C285" s="1" t="s">
+      <c r="C285" s="2" t="s">
         <v>880</v>
       </c>
       <c r="D285" s="1"/>
@@ -11379,7 +11380,7 @@
       <c r="B286" s="1">
         <v>3</v>
       </c>
-      <c r="C286" s="1" t="s">
+      <c r="C286" s="2" t="s">
         <v>883</v>
       </c>
       <c r="D286" s="1"/>
@@ -11401,7 +11402,7 @@
       <c r="B287" s="1">
         <v>3</v>
       </c>
-      <c r="C287" s="1" t="s">
+      <c r="C287" s="2" t="s">
         <v>886</v>
       </c>
       <c r="D287" s="1"/>
@@ -11423,7 +11424,7 @@
       <c r="B288" s="1">
         <v>3</v>
       </c>
-      <c r="C288" s="1" t="s">
+      <c r="C288" s="2" t="s">
         <v>889</v>
       </c>
       <c r="D288" s="1"/>
@@ -11445,7 +11446,7 @@
       <c r="B289" s="1">
         <v>3</v>
       </c>
-      <c r="C289" s="1" t="s">
+      <c r="C289" s="2" t="s">
         <v>892</v>
       </c>
       <c r="D289" s="1"/>
@@ -11467,7 +11468,7 @@
       <c r="B290" s="1">
         <v>3</v>
       </c>
-      <c r="C290" s="1" t="s">
+      <c r="C290" s="2" t="s">
         <v>895</v>
       </c>
       <c r="D290" s="1"/>
@@ -11489,7 +11490,7 @@
       <c r="B291" s="1">
         <v>3</v>
       </c>
-      <c r="C291" s="1" t="s">
+      <c r="C291" s="2" t="s">
         <v>898</v>
       </c>
       <c r="D291" s="1"/>
@@ -11511,7 +11512,7 @@
       <c r="B292" s="1">
         <v>3</v>
       </c>
-      <c r="C292" s="1" t="s">
+      <c r="C292" s="2" t="s">
         <v>901</v>
       </c>
       <c r="D292" s="1"/>
@@ -11533,7 +11534,7 @@
       <c r="B293" s="1">
         <v>3</v>
       </c>
-      <c r="C293" s="1" t="s">
+      <c r="C293" s="2" t="s">
         <v>904</v>
       </c>
       <c r="D293" s="1"/>
@@ -11555,7 +11556,7 @@
       <c r="B294" s="1">
         <v>3</v>
       </c>
-      <c r="C294" s="1" t="s">
+      <c r="C294" s="2" t="s">
         <v>907</v>
       </c>
       <c r="D294" s="1"/>
@@ -11577,7 +11578,7 @@
       <c r="B295" s="1">
         <v>3</v>
       </c>
-      <c r="C295" s="1" t="s">
+      <c r="C295" s="2" t="s">
         <v>910</v>
       </c>
       <c r="D295" s="1"/>
@@ -11599,7 +11600,7 @@
       <c r="B296" s="1">
         <v>3</v>
       </c>
-      <c r="C296" s="1" t="s">
+      <c r="C296" s="2" t="s">
         <v>913</v>
       </c>
       <c r="D296" s="1"/>
@@ -11621,7 +11622,7 @@
       <c r="B297" s="1">
         <v>3</v>
       </c>
-      <c r="C297" s="1" t="s">
+      <c r="C297" s="2" t="s">
         <v>916</v>
       </c>
       <c r="D297" s="1"/>
@@ -11643,7 +11644,7 @@
       <c r="B298" s="1">
         <v>3</v>
       </c>
-      <c r="C298" s="1" t="s">
+      <c r="C298" s="2" t="s">
         <v>919</v>
       </c>
       <c r="D298" s="1"/>
@@ -11665,7 +11666,7 @@
       <c r="B299" s="1">
         <v>3</v>
       </c>
-      <c r="C299" s="1" t="s">
+      <c r="C299" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D299" s="1"/>
@@ -11687,7 +11688,7 @@
       <c r="B300" s="1">
         <v>3</v>
       </c>
-      <c r="C300" s="1" t="s">
+      <c r="C300" s="2" t="s">
         <v>925</v>
       </c>
       <c r="D300" s="1"/>
@@ -11709,7 +11710,7 @@
       <c r="B301" s="1">
         <v>3</v>
       </c>
-      <c r="C301" s="1" t="s">
+      <c r="C301" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D301" s="1"/>
@@ -11731,7 +11732,7 @@
       <c r="B302" s="1">
         <v>3</v>
       </c>
-      <c r="C302" s="1" t="s">
+      <c r="C302" s="2" t="s">
         <v>931</v>
       </c>
       <c r="D302" s="1"/>
@@ -11753,7 +11754,7 @@
       <c r="B303" s="1">
         <v>3</v>
       </c>
-      <c r="C303" s="1" t="s">
+      <c r="C303" s="2" t="s">
         <v>934</v>
       </c>
       <c r="D303" s="1"/>
@@ -11775,7 +11776,7 @@
       <c r="B304" s="1">
         <v>3</v>
       </c>
-      <c r="C304" s="1" t="s">
+      <c r="C304" s="2" t="s">
         <v>937</v>
       </c>
       <c r="D304" s="1"/>
@@ -11797,7 +11798,7 @@
       <c r="B305" s="1">
         <v>3</v>
       </c>
-      <c r="C305" s="1" t="s">
+      <c r="C305" s="2" t="s">
         <v>940</v>
       </c>
       <c r="D305" s="1"/>
@@ -11819,7 +11820,7 @@
       <c r="B306" s="1">
         <v>3</v>
       </c>
-      <c r="C306" s="1" t="s">
+      <c r="C306" s="2" t="s">
         <v>943</v>
       </c>
       <c r="D306" s="1"/>
@@ -11839,7 +11840,7 @@
       <c r="B307" s="1">
         <v>2</v>
       </c>
-      <c r="C307" s="1" t="s">
+      <c r="C307" s="2" t="s">
         <v>946</v>
       </c>
       <c r="D307" s="1" t="s">
@@ -11859,7 +11860,7 @@
       <c r="B308" s="1">
         <v>3</v>
       </c>
-      <c r="C308" s="1" t="s">
+      <c r="C308" s="2" t="s">
         <v>949</v>
       </c>
       <c r="D308" s="1"/>
@@ -11881,7 +11882,7 @@
       <c r="B309" s="1">
         <v>3</v>
       </c>
-      <c r="C309" s="1" t="s">
+      <c r="C309" s="2" t="s">
         <v>952</v>
       </c>
       <c r="D309" s="1"/>
@@ -11903,7 +11904,7 @@
       <c r="B310" s="1">
         <v>3</v>
       </c>
-      <c r="C310" s="1" t="s">
+      <c r="C310" s="2" t="s">
         <v>955</v>
       </c>
       <c r="D310" s="1"/>
@@ -11925,7 +11926,7 @@
       <c r="B311" s="1">
         <v>3</v>
       </c>
-      <c r="C311" s="1" t="s">
+      <c r="C311" s="2" t="s">
         <v>958</v>
       </c>
       <c r="D311" s="1"/>
@@ -11947,7 +11948,7 @@
       <c r="B312" s="1">
         <v>3</v>
       </c>
-      <c r="C312" s="1" t="s">
+      <c r="C312" s="2" t="s">
         <v>961</v>
       </c>
       <c r="D312" s="1"/>
@@ -11969,7 +11970,7 @@
       <c r="B313" s="1">
         <v>3</v>
       </c>
-      <c r="C313" s="1" t="s">
+      <c r="C313" s="2" t="s">
         <v>964</v>
       </c>
       <c r="D313" s="1"/>
@@ -11991,7 +11992,7 @@
       <c r="B314" s="1">
         <v>3</v>
       </c>
-      <c r="C314" s="1" t="s">
+      <c r="C314" s="2" t="s">
         <v>967</v>
       </c>
       <c r="D314" s="1"/>
@@ -12013,7 +12014,7 @@
       <c r="B315" s="1">
         <v>3</v>
       </c>
-      <c r="C315" s="1" t="s">
+      <c r="C315" s="2" t="s">
         <v>970</v>
       </c>
       <c r="D315" s="1"/>
@@ -12035,7 +12036,7 @@
       <c r="B316" s="1">
         <v>3</v>
       </c>
-      <c r="C316" s="1" t="s">
+      <c r="C316" s="2" t="s">
         <v>973</v>
       </c>
       <c r="D316" s="1"/>
@@ -12057,7 +12058,7 @@
       <c r="B317" s="1">
         <v>3</v>
       </c>
-      <c r="C317" s="1" t="s">
+      <c r="C317" s="2" t="s">
         <v>976</v>
       </c>
       <c r="D317" s="1"/>
@@ -12079,7 +12080,7 @@
       <c r="B318" s="1">
         <v>3</v>
       </c>
-      <c r="C318" s="1" t="s">
+      <c r="C318" s="2" t="s">
         <v>979</v>
       </c>
       <c r="D318" s="1"/>
@@ -12101,7 +12102,7 @@
       <c r="B319" s="1">
         <v>3</v>
       </c>
-      <c r="C319" s="1" t="s">
+      <c r="C319" s="2" t="s">
         <v>982</v>
       </c>
       <c r="D319" s="1"/>
@@ -12121,7 +12122,7 @@
       <c r="B320" s="1">
         <v>2</v>
       </c>
-      <c r="C320" s="1" t="s">
+      <c r="C320" s="2" t="s">
         <v>985</v>
       </c>
       <c r="D320" s="1" t="s">
@@ -12141,7 +12142,7 @@
       <c r="B321" s="1">
         <v>3</v>
       </c>
-      <c r="C321" s="1" t="s">
+      <c r="C321" s="2" t="s">
         <v>988</v>
       </c>
       <c r="D321" s="1"/>
@@ -12163,7 +12164,7 @@
       <c r="B322" s="1">
         <v>3</v>
       </c>
-      <c r="C322" s="1" t="s">
+      <c r="C322" s="2" t="s">
         <v>991</v>
       </c>
       <c r="D322" s="1"/>
@@ -12185,7 +12186,7 @@
       <c r="B323" s="1">
         <v>3</v>
       </c>
-      <c r="C323" s="1" t="s">
+      <c r="C323" s="2" t="s">
         <v>994</v>
       </c>
       <c r="D323" s="1"/>
@@ -12207,7 +12208,7 @@
       <c r="B324" s="1">
         <v>3</v>
       </c>
-      <c r="C324" s="1" t="s">
+      <c r="C324" s="2" t="s">
         <v>997</v>
       </c>
       <c r="D324" s="1"/>
@@ -12229,7 +12230,7 @@
       <c r="B325" s="1">
         <v>3</v>
       </c>
-      <c r="C325" s="1" t="s">
+      <c r="C325" s="2" t="s">
         <v>1000</v>
       </c>
       <c r="D325" s="1"/>
@@ -12251,7 +12252,7 @@
       <c r="B326" s="1">
         <v>3</v>
       </c>
-      <c r="C326" s="1" t="s">
+      <c r="C326" s="2" t="s">
         <v>1003</v>
       </c>
       <c r="D326" s="1"/>
@@ -12273,7 +12274,7 @@
       <c r="B327" s="1">
         <v>3</v>
       </c>
-      <c r="C327" s="1" t="s">
+      <c r="C327" s="2" t="s">
         <v>1006</v>
       </c>
       <c r="D327" s="1"/>
@@ -12295,7 +12296,7 @@
       <c r="B328" s="1">
         <v>3</v>
       </c>
-      <c r="C328" s="1" t="s">
+      <c r="C328" s="2" t="s">
         <v>1009</v>
       </c>
       <c r="D328" s="1"/>
@@ -12317,7 +12318,7 @@
       <c r="B329" s="1">
         <v>3</v>
       </c>
-      <c r="C329" s="1" t="s">
+      <c r="C329" s="2" t="s">
         <v>1012</v>
       </c>
       <c r="D329" s="1"/>
@@ -12339,7 +12340,7 @@
       <c r="B330" s="1">
         <v>3</v>
       </c>
-      <c r="C330" s="1" t="s">
+      <c r="C330" s="2" t="s">
         <v>1015</v>
       </c>
       <c r="D330" s="1"/>
@@ -12361,7 +12362,7 @@
       <c r="B331" s="1">
         <v>3</v>
       </c>
-      <c r="C331" s="1" t="s">
+      <c r="C331" s="2" t="s">
         <v>1018</v>
       </c>
       <c r="D331" s="1"/>
@@ -12383,7 +12384,7 @@
       <c r="B332" s="1">
         <v>3</v>
       </c>
-      <c r="C332" s="1" t="s">
+      <c r="C332" s="2" t="s">
         <v>1021</v>
       </c>
       <c r="D332" s="1"/>
@@ -12405,7 +12406,7 @@
       <c r="B333" s="1">
         <v>3</v>
       </c>
-      <c r="C333" s="1" t="s">
+      <c r="C333" s="2" t="s">
         <v>1024</v>
       </c>
       <c r="D333" s="1"/>
@@ -12427,7 +12428,7 @@
       <c r="B334" s="1">
         <v>3</v>
       </c>
-      <c r="C334" s="1" t="s">
+      <c r="C334" s="2" t="s">
         <v>1027</v>
       </c>
       <c r="D334" s="1"/>
@@ -12449,7 +12450,7 @@
       <c r="B335" s="1">
         <v>3</v>
       </c>
-      <c r="C335" s="1" t="s">
+      <c r="C335" s="2" t="s">
         <v>1030</v>
       </c>
       <c r="D335" s="1"/>
@@ -12471,7 +12472,7 @@
       <c r="B336" s="1">
         <v>3</v>
       </c>
-      <c r="C336" s="1" t="s">
+      <c r="C336" s="2" t="s">
         <v>1033</v>
       </c>
       <c r="D336" s="1"/>
@@ -12493,7 +12494,7 @@
       <c r="B337" s="1">
         <v>3</v>
       </c>
-      <c r="C337" s="1" t="s">
+      <c r="C337" s="2" t="s">
         <v>1036</v>
       </c>
       <c r="D337" s="1"/>
@@ -12515,7 +12516,7 @@
       <c r="B338" s="1">
         <v>3</v>
       </c>
-      <c r="C338" s="1" t="s">
+      <c r="C338" s="2" t="s">
         <v>1039</v>
       </c>
       <c r="D338" s="1"/>
@@ -12537,7 +12538,7 @@
       <c r="B339" s="1">
         <v>3</v>
       </c>
-      <c r="C339" s="1" t="s">
+      <c r="C339" s="2" t="s">
         <v>1042</v>
       </c>
       <c r="D339" s="1"/>
@@ -12559,7 +12560,7 @@
       <c r="B340" s="1">
         <v>3</v>
       </c>
-      <c r="C340" s="1" t="s">
+      <c r="C340" s="2" t="s">
         <v>1045</v>
       </c>
       <c r="D340" s="1"/>
@@ -12581,7 +12582,7 @@
       <c r="B341" s="1">
         <v>3</v>
       </c>
-      <c r="C341" s="1" t="s">
+      <c r="C341" s="2" t="s">
         <v>1048</v>
       </c>
       <c r="D341" s="1"/>
@@ -12603,7 +12604,7 @@
       <c r="B342" s="1">
         <v>3</v>
       </c>
-      <c r="C342" s="1" t="s">
+      <c r="C342" s="2" t="s">
         <v>1051</v>
       </c>
       <c r="D342" s="1"/>
@@ -12625,7 +12626,7 @@
       <c r="B343" s="1">
         <v>3</v>
       </c>
-      <c r="C343" s="1" t="s">
+      <c r="C343" s="2" t="s">
         <v>1054</v>
       </c>
       <c r="D343" s="1"/>
@@ -12647,7 +12648,7 @@
       <c r="B344" s="1">
         <v>3</v>
       </c>
-      <c r="C344" s="1" t="s">
+      <c r="C344" s="2" t="s">
         <v>1057</v>
       </c>
       <c r="D344" s="1"/>
@@ -12669,7 +12670,7 @@
       <c r="B345" s="1">
         <v>3</v>
       </c>
-      <c r="C345" s="1" t="s">
+      <c r="C345" s="2" t="s">
         <v>1060</v>
       </c>
       <c r="D345" s="1"/>
@@ -12691,7 +12692,7 @@
       <c r="B346" s="1">
         <v>3</v>
       </c>
-      <c r="C346" s="1" t="s">
+      <c r="C346" s="2" t="s">
         <v>1063</v>
       </c>
       <c r="D346" s="1"/>
@@ -12713,7 +12714,7 @@
       <c r="B347" s="1">
         <v>3</v>
       </c>
-      <c r="C347" s="1" t="s">
+      <c r="C347" s="2" t="s">
         <v>1066</v>
       </c>
       <c r="D347" s="1"/>
@@ -12735,7 +12736,7 @@
       <c r="B348" s="1">
         <v>3</v>
       </c>
-      <c r="C348" s="1" t="s">
+      <c r="C348" s="2" t="s">
         <v>1069</v>
       </c>
       <c r="D348" s="1"/>
@@ -12757,7 +12758,7 @@
       <c r="B349" s="1">
         <v>3</v>
       </c>
-      <c r="C349" s="1" t="s">
+      <c r="C349" s="2" t="s">
         <v>1072</v>
       </c>
       <c r="D349" s="1"/>
@@ -12779,7 +12780,7 @@
       <c r="B350" s="1">
         <v>3</v>
       </c>
-      <c r="C350" s="1" t="s">
+      <c r="C350" s="2" t="s">
         <v>1075</v>
       </c>
       <c r="D350" s="1"/>
@@ -12801,7 +12802,7 @@
       <c r="B351" s="1">
         <v>3</v>
       </c>
-      <c r="C351" s="1" t="s">
+      <c r="C351" s="2" t="s">
         <v>1078</v>
       </c>
       <c r="D351" s="1"/>
@@ -12823,7 +12824,7 @@
       <c r="B352" s="1">
         <v>3</v>
       </c>
-      <c r="C352" s="1" t="s">
+      <c r="C352" s="2" t="s">
         <v>1081</v>
       </c>
       <c r="D352" s="1"/>
@@ -12845,7 +12846,7 @@
       <c r="B353" s="1">
         <v>3</v>
       </c>
-      <c r="C353" s="1" t="s">
+      <c r="C353" s="2" t="s">
         <v>1084</v>
       </c>
       <c r="D353" s="1"/>
@@ -12867,7 +12868,7 @@
       <c r="B354" s="1">
         <v>3</v>
       </c>
-      <c r="C354" s="1" t="s">
+      <c r="C354" s="2" t="s">
         <v>1087</v>
       </c>
       <c r="D354" s="1"/>
@@ -12889,7 +12890,7 @@
       <c r="B355" s="1">
         <v>3</v>
       </c>
-      <c r="C355" s="1" t="s">
+      <c r="C355" s="2" t="s">
         <v>1090</v>
       </c>
       <c r="D355" s="1"/>
@@ -12909,7 +12910,7 @@
       <c r="B356" s="1">
         <v>2</v>
       </c>
-      <c r="C356" s="1" t="s">
+      <c r="C356" s="2" t="s">
         <v>1093</v>
       </c>
       <c r="D356" s="1" t="s">
@@ -12929,7 +12930,7 @@
       <c r="B357" s="1">
         <v>3</v>
       </c>
-      <c r="C357" s="1" t="s">
+      <c r="C357" s="2" t="s">
         <v>1096</v>
       </c>
       <c r="D357" s="1"/>
@@ -12951,7 +12952,7 @@
       <c r="B358" s="1">
         <v>3</v>
       </c>
-      <c r="C358" s="1" t="s">
+      <c r="C358" s="2" t="s">
         <v>1099</v>
       </c>
       <c r="D358" s="1"/>
@@ -12973,7 +12974,7 @@
       <c r="B359" s="1">
         <v>3</v>
       </c>
-      <c r="C359" s="1" t="s">
+      <c r="C359" s="2" t="s">
         <v>1102</v>
       </c>
       <c r="D359" s="1"/>
@@ -12995,7 +12996,7 @@
       <c r="B360" s="1">
         <v>3</v>
       </c>
-      <c r="C360" s="1" t="s">
+      <c r="C360" s="2" t="s">
         <v>1105</v>
       </c>
       <c r="D360" s="1"/>
@@ -13017,7 +13018,7 @@
       <c r="B361" s="1">
         <v>3</v>
       </c>
-      <c r="C361" s="1" t="s">
+      <c r="C361" s="2" t="s">
         <v>1108</v>
       </c>
       <c r="D361" s="1"/>
@@ -13039,7 +13040,7 @@
       <c r="B362" s="1">
         <v>3</v>
       </c>
-      <c r="C362" s="1" t="s">
+      <c r="C362" s="2" t="s">
         <v>1111</v>
       </c>
       <c r="D362" s="1"/>
@@ -13061,7 +13062,7 @@
       <c r="B363" s="1">
         <v>3</v>
       </c>
-      <c r="C363" s="1" t="s">
+      <c r="C363" s="2" t="s">
         <v>1114</v>
       </c>
       <c r="D363" s="1"/>
@@ -13083,7 +13084,7 @@
       <c r="B364" s="1">
         <v>3</v>
       </c>
-      <c r="C364" s="1" t="s">
+      <c r="C364" s="2" t="s">
         <v>1117</v>
       </c>
       <c r="D364" s="1"/>
@@ -13105,7 +13106,7 @@
       <c r="B365" s="1">
         <v>3</v>
       </c>
-      <c r="C365" s="1" t="s">
+      <c r="C365" s="2" t="s">
         <v>1120</v>
       </c>
       <c r="D365" s="1"/>
@@ -13127,7 +13128,7 @@
       <c r="B366" s="1">
         <v>3</v>
       </c>
-      <c r="C366" s="1" t="s">
+      <c r="C366" s="2" t="s">
         <v>1123</v>
       </c>
       <c r="D366" s="1"/>
@@ -13149,7 +13150,7 @@
       <c r="B367" s="1">
         <v>3</v>
       </c>
-      <c r="C367" s="1" t="s">
+      <c r="C367" s="2" t="s">
         <v>1126</v>
       </c>
       <c r="D367" s="1"/>
@@ -13171,7 +13172,7 @@
       <c r="B368" s="1">
         <v>3</v>
       </c>
-      <c r="C368" s="1" t="s">
+      <c r="C368" s="2" t="s">
         <v>1129</v>
       </c>
       <c r="D368" s="1"/>
@@ -13191,7 +13192,7 @@
       <c r="B369" s="1">
         <v>2</v>
       </c>
-      <c r="C369" s="1" t="s">
+      <c r="C369" s="2" t="s">
         <v>1132</v>
       </c>
       <c r="D369" s="1" t="s">
@@ -13211,7 +13212,7 @@
       <c r="B370" s="1">
         <v>3</v>
       </c>
-      <c r="C370" s="1" t="s">
+      <c r="C370" s="2" t="s">
         <v>1135</v>
       </c>
       <c r="D370" s="1"/>
@@ -13233,7 +13234,7 @@
       <c r="B371" s="1">
         <v>3</v>
       </c>
-      <c r="C371" s="1" t="s">
+      <c r="C371" s="2" t="s">
         <v>1138</v>
       </c>
       <c r="D371" s="1"/>
@@ -13255,7 +13256,7 @@
       <c r="B372" s="1">
         <v>3</v>
       </c>
-      <c r="C372" s="1" t="s">
+      <c r="C372" s="2" t="s">
         <v>1141</v>
       </c>
       <c r="D372" s="1"/>
@@ -13277,7 +13278,7 @@
       <c r="B373" s="1">
         <v>3</v>
       </c>
-      <c r="C373" s="1" t="s">
+      <c r="C373" s="2" t="s">
         <v>1144</v>
       </c>
       <c r="D373" s="1"/>
@@ -13299,7 +13300,7 @@
       <c r="B374" s="1">
         <v>3</v>
       </c>
-      <c r="C374" s="1" t="s">
+      <c r="C374" s="2" t="s">
         <v>1147</v>
       </c>
       <c r="D374" s="1"/>
@@ -13321,7 +13322,7 @@
       <c r="B375" s="1">
         <v>3</v>
       </c>
-      <c r="C375" s="1" t="s">
+      <c r="C375" s="2" t="s">
         <v>1150</v>
       </c>
       <c r="D375" s="1"/>
@@ -13343,7 +13344,7 @@
       <c r="B376" s="1">
         <v>3</v>
       </c>
-      <c r="C376" s="1" t="s">
+      <c r="C376" s="2" t="s">
         <v>1153</v>
       </c>
       <c r="D376" s="1"/>
@@ -13365,7 +13366,7 @@
       <c r="B377" s="1">
         <v>3</v>
       </c>
-      <c r="C377" s="1" t="s">
+      <c r="C377" s="2" t="s">
         <v>1156</v>
       </c>
       <c r="D377" s="1"/>
@@ -13387,7 +13388,7 @@
       <c r="B378" s="1">
         <v>3</v>
       </c>
-      <c r="C378" s="1" t="s">
+      <c r="C378" s="2" t="s">
         <v>1159</v>
       </c>
       <c r="D378" s="1"/>
@@ -13407,7 +13408,7 @@
       <c r="B379" s="1">
         <v>2</v>
       </c>
-      <c r="C379" s="1" t="s">
+      <c r="C379" s="2" t="s">
         <v>1162</v>
       </c>
       <c r="D379" s="1" t="s">
@@ -13427,7 +13428,7 @@
       <c r="B380" s="1">
         <v>3</v>
       </c>
-      <c r="C380" s="1" t="s">
+      <c r="C380" s="2" t="s">
         <v>1165</v>
       </c>
       <c r="D380" s="1"/>
@@ -13449,7 +13450,7 @@
       <c r="B381" s="1">
         <v>3</v>
       </c>
-      <c r="C381" s="1" t="s">
+      <c r="C381" s="2" t="s">
         <v>1168</v>
       </c>
       <c r="D381" s="1"/>
@@ -13471,7 +13472,7 @@
       <c r="B382" s="1">
         <v>3</v>
       </c>
-      <c r="C382" s="1" t="s">
+      <c r="C382" s="2" t="s">
         <v>1171</v>
       </c>
       <c r="D382" s="1"/>
@@ -13493,7 +13494,7 @@
       <c r="B383" s="1">
         <v>3</v>
       </c>
-      <c r="C383" s="1" t="s">
+      <c r="C383" s="2" t="s">
         <v>1174</v>
       </c>
       <c r="D383" s="1"/>
@@ -13515,7 +13516,7 @@
       <c r="B384" s="1">
         <v>3</v>
       </c>
-      <c r="C384" s="1" t="s">
+      <c r="C384" s="2" t="s">
         <v>1177</v>
       </c>
       <c r="D384" s="1"/>
@@ -13537,7 +13538,7 @@
       <c r="B385" s="1">
         <v>3</v>
       </c>
-      <c r="C385" s="1" t="s">
+      <c r="C385" s="2" t="s">
         <v>1180</v>
       </c>
       <c r="D385" s="1"/>
@@ -13559,7 +13560,7 @@
       <c r="B386" s="1">
         <v>3</v>
       </c>
-      <c r="C386" s="1" t="s">
+      <c r="C386" s="2" t="s">
         <v>1183</v>
       </c>
       <c r="D386" s="1"/>
@@ -13581,7 +13582,7 @@
       <c r="B387" s="1">
         <v>3</v>
       </c>
-      <c r="C387" s="1" t="s">
+      <c r="C387" s="2" t="s">
         <v>1186</v>
       </c>
       <c r="D387" s="1"/>
@@ -13603,7 +13604,7 @@
       <c r="B388" s="1">
         <v>3</v>
       </c>
-      <c r="C388" s="1" t="s">
+      <c r="C388" s="2" t="s">
         <v>1189</v>
       </c>
       <c r="D388" s="1"/>
@@ -13625,7 +13626,7 @@
       <c r="B389" s="1">
         <v>3</v>
       </c>
-      <c r="C389" s="1" t="s">
+      <c r="C389" s="2" t="s">
         <v>1192</v>
       </c>
       <c r="D389" s="1"/>
@@ -13647,7 +13648,7 @@
       <c r="B390" s="1">
         <v>3</v>
       </c>
-      <c r="C390" s="1" t="s">
+      <c r="C390" s="2" t="s">
         <v>1195</v>
       </c>
       <c r="D390" s="1"/>
@@ -13669,7 +13670,7 @@
       <c r="B391" s="1">
         <v>3</v>
       </c>
-      <c r="C391" s="1" t="s">
+      <c r="C391" s="2" t="s">
         <v>1198</v>
       </c>
       <c r="D391" s="1"/>
@@ -13691,7 +13692,7 @@
       <c r="B392" s="1">
         <v>3</v>
       </c>
-      <c r="C392" s="1" t="s">
+      <c r="C392" s="2" t="s">
         <v>1201</v>
       </c>
       <c r="D392" s="1"/>
@@ -13713,7 +13714,7 @@
       <c r="B393" s="1">
         <v>3</v>
       </c>
-      <c r="C393" s="1" t="s">
+      <c r="C393" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="D393" s="1"/>
@@ -13735,7 +13736,7 @@
       <c r="B394" s="1">
         <v>3</v>
       </c>
-      <c r="C394" s="1" t="s">
+      <c r="C394" s="2" t="s">
         <v>1207</v>
       </c>
       <c r="D394" s="1"/>
@@ -13757,7 +13758,7 @@
       <c r="B395" s="1">
         <v>3</v>
       </c>
-      <c r="C395" s="1" t="s">
+      <c r="C395" s="2" t="s">
         <v>1210</v>
       </c>
       <c r="D395" s="1"/>
@@ -13779,7 +13780,7 @@
       <c r="B396" s="1">
         <v>3</v>
       </c>
-      <c r="C396" s="1" t="s">
+      <c r="C396" s="2" t="s">
         <v>1213</v>
       </c>
       <c r="D396" s="1"/>
@@ -13801,7 +13802,7 @@
       <c r="B397" s="1">
         <v>3</v>
       </c>
-      <c r="C397" s="1" t="s">
+      <c r="C397" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="D397" s="1"/>
@@ -13823,7 +13824,7 @@
       <c r="B398" s="1">
         <v>3</v>
       </c>
-      <c r="C398" s="1" t="s">
+      <c r="C398" s="2" t="s">
         <v>1219</v>
       </c>
       <c r="D398" s="1"/>
@@ -13845,7 +13846,7 @@
       <c r="B399" s="1">
         <v>3</v>
       </c>
-      <c r="C399" s="1" t="s">
+      <c r="C399" s="2" t="s">
         <v>1222</v>
       </c>
       <c r="D399" s="1"/>
@@ -13867,7 +13868,7 @@
       <c r="B400" s="1">
         <v>3</v>
       </c>
-      <c r="C400" s="1" t="s">
+      <c r="C400" s="2" t="s">
         <v>1225</v>
       </c>
       <c r="D400" s="1"/>
@@ -13889,7 +13890,7 @@
       <c r="B401" s="1">
         <v>3</v>
       </c>
-      <c r="C401" s="1" t="s">
+      <c r="C401" s="2" t="s">
         <v>1228</v>
       </c>
       <c r="D401" s="1"/>
@@ -13909,7 +13910,7 @@
       <c r="B402" s="1">
         <v>2</v>
       </c>
-      <c r="C402" s="1" t="s">
+      <c r="C402" s="2" t="s">
         <v>1231</v>
       </c>
       <c r="D402" s="1" t="s">
@@ -13929,7 +13930,7 @@
       <c r="B403" s="1">
         <v>3</v>
       </c>
-      <c r="C403" s="1" t="s">
+      <c r="C403" s="2" t="s">
         <v>1234</v>
       </c>
       <c r="D403" s="1"/>
@@ -13951,7 +13952,7 @@
       <c r="B404" s="1">
         <v>3</v>
       </c>
-      <c r="C404" s="1" t="s">
+      <c r="C404" s="2" t="s">
         <v>1237</v>
       </c>
       <c r="D404" s="1"/>
@@ -13973,7 +13974,7 @@
       <c r="B405" s="1">
         <v>3</v>
       </c>
-      <c r="C405" s="1" t="s">
+      <c r="C405" s="2" t="s">
         <v>1240</v>
       </c>
       <c r="D405" s="1"/>
@@ -13995,7 +13996,7 @@
       <c r="B406" s="1">
         <v>3</v>
       </c>
-      <c r="C406" s="1" t="s">
+      <c r="C406" s="2" t="s">
         <v>1243</v>
       </c>
       <c r="D406" s="1"/>
@@ -14015,16 +14016,16 @@
       <c r="B407" s="1">
         <v>2</v>
       </c>
-      <c r="C407" s="1" t="s">
+      <c r="C407" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D407" s="1" t="s">
         <v>1246</v>
-      </c>
-      <c r="D407" s="1" t="s">
-        <v>1247</v>
       </c>
       <c r="E407" s="1"/>
       <c r="F407" s="1"/>
       <c r="G407" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H407" s="1"/>
     </row>
@@ -14035,19 +14036,19 @@
       <c r="B408" s="1">
         <v>3</v>
       </c>
-      <c r="C408" s="1" t="s">
-        <v>1249</v>
+      <c r="C408" s="2" t="s">
+        <v>1248</v>
       </c>
       <c r="D408" s="1"/>
       <c r="E408" s="1" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F408" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G408" s="1"/>
       <c r="H408" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="409" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14057,19 +14058,19 @@
       <c r="B409" s="1">
         <v>3</v>
       </c>
-      <c r="C409" s="1" t="s">
-        <v>1252</v>
+      <c r="C409" s="2" t="s">
+        <v>1251</v>
       </c>
       <c r="D409" s="1"/>
       <c r="E409" s="1" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F409" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G409" s="1"/>
       <c r="H409" s="1" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.3">
@@ -14079,19 +14080,19 @@
       <c r="B410" s="1">
         <v>3</v>
       </c>
-      <c r="C410" s="1" t="s">
-        <v>1255</v>
+      <c r="C410" s="2" t="s">
+        <v>1254</v>
       </c>
       <c r="D410" s="1"/>
       <c r="E410" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F410" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G410" s="1"/>
       <c r="H410" s="1" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="411" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -14101,19 +14102,19 @@
       <c r="B411" s="1">
         <v>3</v>
       </c>
-      <c r="C411" s="1" t="s">
-        <v>1258</v>
+      <c r="C411" s="2" t="s">
+        <v>1257</v>
       </c>
       <c r="D411" s="1"/>
       <c r="E411" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F411" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G411" s="1"/>
       <c r="H411" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.3">
@@ -14121,16 +14122,16 @@
       <c r="B412" s="1">
         <v>2</v>
       </c>
-      <c r="C412" s="1" t="s">
+      <c r="C412" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D412" s="1" t="s">
         <v>1261</v>
-      </c>
-      <c r="D412" s="1" t="s">
-        <v>1262</v>
       </c>
       <c r="E412" s="1"/>
       <c r="F412" s="1"/>
       <c r="G412" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H412" s="1"/>
     </row>
@@ -14141,19 +14142,19 @@
       <c r="B413" s="1">
         <v>3</v>
       </c>
-      <c r="C413" s="1" t="s">
-        <v>1264</v>
+      <c r="C413" s="2" t="s">
+        <v>1263</v>
       </c>
       <c r="D413" s="1"/>
       <c r="E413" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="F413" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G413" s="1"/>
       <c r="H413" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="414" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14163,19 +14164,19 @@
       <c r="B414" s="1">
         <v>3</v>
       </c>
-      <c r="C414" s="1" t="s">
-        <v>1267</v>
+      <c r="C414" s="2" t="s">
+        <v>1266</v>
       </c>
       <c r="D414" s="1"/>
       <c r="E414" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F414" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G414" s="1"/>
       <c r="H414" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.3">
@@ -14183,16 +14184,16 @@
       <c r="B415" s="1">
         <v>2</v>
       </c>
-      <c r="C415" s="1" t="s">
+      <c r="C415" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D415" s="1" t="s">
         <v>1270</v>
-      </c>
-      <c r="D415" s="1" t="s">
-        <v>1271</v>
       </c>
       <c r="E415" s="1"/>
       <c r="F415" s="1"/>
       <c r="G415" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H415" s="1"/>
     </row>
@@ -14203,19 +14204,19 @@
       <c r="B416" s="1">
         <v>3</v>
       </c>
-      <c r="C416" s="1" t="s">
-        <v>1273</v>
+      <c r="C416" s="2" t="s">
+        <v>1272</v>
       </c>
       <c r="D416" s="1"/>
       <c r="E416" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F416" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G416" s="1"/>
       <c r="H416" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="417" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -14225,19 +14226,19 @@
       <c r="B417" s="1">
         <v>3</v>
       </c>
-      <c r="C417" s="1" t="s">
-        <v>1276</v>
+      <c r="C417" s="2" t="s">
+        <v>1275</v>
       </c>
       <c r="D417" s="1"/>
       <c r="E417" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="F417" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G417" s="1"/>
       <c r="H417" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="418" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -14247,19 +14248,19 @@
       <c r="B418" s="1">
         <v>3</v>
       </c>
-      <c r="C418" s="1" t="s">
-        <v>1279</v>
+      <c r="C418" s="2" t="s">
+        <v>1278</v>
       </c>
       <c r="D418" s="1"/>
       <c r="E418" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F418" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G418" s="1"/>
       <c r="H418" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.3">
@@ -14269,19 +14270,19 @@
       <c r="B419" s="1">
         <v>3</v>
       </c>
-      <c r="C419" s="1" t="s">
-        <v>1282</v>
+      <c r="C419" s="2" t="s">
+        <v>1281</v>
       </c>
       <c r="D419" s="1"/>
       <c r="E419" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F419" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G419" s="1"/>
       <c r="H419" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="420" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -14291,19 +14292,19 @@
       <c r="B420" s="1">
         <v>3</v>
       </c>
-      <c r="C420" s="1" t="s">
-        <v>1285</v>
+      <c r="C420" s="2" t="s">
+        <v>1284</v>
       </c>
       <c r="D420" s="1"/>
       <c r="E420" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F420" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G420" s="1"/>
       <c r="H420" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.3">
@@ -14313,19 +14314,19 @@
       <c r="B421" s="1">
         <v>3</v>
       </c>
-      <c r="C421" s="1" t="s">
-        <v>1288</v>
+      <c r="C421" s="2" t="s">
+        <v>1287</v>
       </c>
       <c r="D421" s="1"/>
       <c r="E421" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F421" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G421" s="1"/>
       <c r="H421" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="422" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -14335,19 +14336,19 @@
       <c r="B422" s="1">
         <v>3</v>
       </c>
-      <c r="C422" s="1" t="s">
-        <v>1291</v>
+      <c r="C422" s="2" t="s">
+        <v>1290</v>
       </c>
       <c r="D422" s="1"/>
       <c r="E422" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="F422" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G422" s="1"/>
       <c r="H422" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="423" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -14357,19 +14358,19 @@
       <c r="B423" s="1">
         <v>3</v>
       </c>
-      <c r="C423" s="1" t="s">
-        <v>1294</v>
+      <c r="C423" s="2" t="s">
+        <v>1293</v>
       </c>
       <c r="D423" s="1"/>
       <c r="E423" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="F423" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G423" s="1"/>
       <c r="H423" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.3">
@@ -14377,16 +14378,16 @@
       <c r="B424" s="1">
         <v>2</v>
       </c>
-      <c r="C424" s="1" t="s">
+      <c r="C424" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D424" s="1" t="s">
         <v>1297</v>
-      </c>
-      <c r="D424" s="1" t="s">
-        <v>1298</v>
       </c>
       <c r="E424" s="1"/>
       <c r="F424" s="1"/>
       <c r="G424" s="1" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H424" s="1"/>
     </row>
@@ -14397,19 +14398,19 @@
       <c r="B425" s="1">
         <v>3</v>
       </c>
-      <c r="C425" s="1" t="s">
-        <v>1300</v>
+      <c r="C425" s="2" t="s">
+        <v>1299</v>
       </c>
       <c r="D425" s="1"/>
       <c r="E425" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="F425" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G425" s="1"/>
       <c r="H425" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="426" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -14419,19 +14420,19 @@
       <c r="B426" s="1">
         <v>3</v>
       </c>
-      <c r="C426" s="1" t="s">
-        <v>1303</v>
+      <c r="C426" s="2" t="s">
+        <v>1302</v>
       </c>
       <c r="D426" s="1"/>
       <c r="E426" s="1" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="F426" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G426" s="1"/>
       <c r="H426" s="1" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.3">
@@ -14441,19 +14442,19 @@
       <c r="B427" s="1">
         <v>3</v>
       </c>
-      <c r="C427" s="1" t="s">
-        <v>1306</v>
+      <c r="C427" s="2" t="s">
+        <v>1305</v>
       </c>
       <c r="D427" s="1"/>
       <c r="E427" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F427" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G427" s="1"/>
       <c r="H427" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="428" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -14463,19 +14464,19 @@
       <c r="B428" s="1">
         <v>3</v>
       </c>
-      <c r="C428" s="1" t="s">
-        <v>1309</v>
+      <c r="C428" s="2" t="s">
+        <v>1308</v>
       </c>
       <c r="D428" s="1"/>
       <c r="E428" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="F428" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G428" s="1"/>
       <c r="H428" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="429" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14485,19 +14486,19 @@
       <c r="B429" s="1">
         <v>3</v>
       </c>
-      <c r="C429" s="1" t="s">
-        <v>1312</v>
+      <c r="C429" s="2" t="s">
+        <v>1311</v>
       </c>
       <c r="D429" s="1"/>
       <c r="E429" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="F429" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G429" s="1"/>
       <c r="H429" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="430" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14507,19 +14508,19 @@
       <c r="B430" s="1">
         <v>3</v>
       </c>
-      <c r="C430" s="1" t="s">
-        <v>1315</v>
+      <c r="C430" s="2" t="s">
+        <v>1314</v>
       </c>
       <c r="D430" s="1"/>
       <c r="E430" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F430" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G430" s="1"/>
       <c r="H430" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.3">
@@ -14529,19 +14530,19 @@
       <c r="B431" s="1">
         <v>3</v>
       </c>
-      <c r="C431" s="1" t="s">
-        <v>1318</v>
+      <c r="C431" s="2" t="s">
+        <v>1317</v>
       </c>
       <c r="D431" s="1"/>
       <c r="E431" s="1" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="F431" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G431" s="1"/>
       <c r="H431" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="432" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -14551,19 +14552,19 @@
       <c r="B432" s="1">
         <v>3</v>
       </c>
-      <c r="C432" s="1" t="s">
-        <v>1321</v>
+      <c r="C432" s="2" t="s">
+        <v>1320</v>
       </c>
       <c r="D432" s="1"/>
       <c r="E432" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F432" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G432" s="1"/>
       <c r="H432" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="433" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14573,19 +14574,19 @@
       <c r="B433" s="1">
         <v>3</v>
       </c>
-      <c r="C433" s="1" t="s">
-        <v>1323</v>
+      <c r="C433" s="2" t="s">
+        <v>1322</v>
       </c>
       <c r="D433" s="1"/>
       <c r="E433" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="F433" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G433" s="1"/>
       <c r="H433" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="434" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14595,19 +14596,19 @@
       <c r="B434" s="1">
         <v>3</v>
       </c>
-      <c r="C434" s="1" t="s">
-        <v>1326</v>
+      <c r="C434" s="2" t="s">
+        <v>1325</v>
       </c>
       <c r="D434" s="1"/>
       <c r="E434" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="F434" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G434" s="1"/>
       <c r="H434" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.3">
@@ -14615,16 +14616,16 @@
       <c r="B435" s="1">
         <v>2</v>
       </c>
-      <c r="C435" s="1" t="s">
+      <c r="C435" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D435" s="1" t="s">
         <v>1329</v>
-      </c>
-      <c r="D435" s="1" t="s">
-        <v>1330</v>
       </c>
       <c r="E435" s="1"/>
       <c r="F435" s="1"/>
       <c r="G435" s="1" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H435" s="1"/>
     </row>
@@ -14635,19 +14636,19 @@
       <c r="B436" s="1">
         <v>3</v>
       </c>
-      <c r="C436" s="1" t="s">
-        <v>1332</v>
+      <c r="C436" s="2" t="s">
+        <v>1331</v>
       </c>
       <c r="D436" s="1"/>
       <c r="E436" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F436" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G436" s="1"/>
       <c r="H436" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="437" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -14657,19 +14658,19 @@
       <c r="B437" s="1">
         <v>3</v>
       </c>
-      <c r="C437" s="1" t="s">
-        <v>1335</v>
+      <c r="C437" s="2" t="s">
+        <v>1334</v>
       </c>
       <c r="D437" s="1"/>
       <c r="E437" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F437" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G437" s="1"/>
       <c r="H437" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="438" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -14679,19 +14680,19 @@
       <c r="B438" s="1">
         <v>3</v>
       </c>
-      <c r="C438" s="1" t="s">
-        <v>1338</v>
+      <c r="C438" s="2" t="s">
+        <v>1337</v>
       </c>
       <c r="D438" s="1"/>
       <c r="E438" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="F438" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G438" s="1"/>
       <c r="H438" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="439" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -14701,19 +14702,19 @@
       <c r="B439" s="1">
         <v>3</v>
       </c>
-      <c r="C439" s="1" t="s">
-        <v>1341</v>
+      <c r="C439" s="2" t="s">
+        <v>1340</v>
       </c>
       <c r="D439" s="1"/>
       <c r="E439" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F439" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G439" s="1"/>
       <c r="H439" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="440" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14723,19 +14724,19 @@
       <c r="B440" s="1">
         <v>3</v>
       </c>
-      <c r="C440" s="1" t="s">
-        <v>1344</v>
+      <c r="C440" s="2" t="s">
+        <v>1343</v>
       </c>
       <c r="D440" s="1"/>
       <c r="E440" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F440" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G440" s="1"/>
       <c r="H440" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="441" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14745,19 +14746,19 @@
       <c r="B441" s="1">
         <v>3</v>
       </c>
-      <c r="C441" s="1" t="s">
-        <v>1347</v>
+      <c r="C441" s="2" t="s">
+        <v>1346</v>
       </c>
       <c r="D441" s="1"/>
       <c r="E441" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="F441" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G441" s="1"/>
       <c r="H441" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="442" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -14767,19 +14768,19 @@
       <c r="B442" s="1">
         <v>3</v>
       </c>
-      <c r="C442" s="1" t="s">
-        <v>1350</v>
+      <c r="C442" s="2" t="s">
+        <v>1349</v>
       </c>
       <c r="D442" s="1"/>
       <c r="E442" s="1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F442" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G442" s="1"/>
       <c r="H442" s="1" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="443" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14789,19 +14790,19 @@
       <c r="B443" s="1">
         <v>3</v>
       </c>
-      <c r="C443" s="1" t="s">
-        <v>1353</v>
+      <c r="C443" s="2" t="s">
+        <v>1352</v>
       </c>
       <c r="D443" s="1"/>
       <c r="E443" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="F443" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G443" s="1"/>
       <c r="H443" s="1" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.3">
@@ -14809,16 +14810,16 @@
       <c r="B444" s="1">
         <v>2</v>
       </c>
-      <c r="C444" s="1" t="s">
+      <c r="C444" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D444" s="1" t="s">
         <v>1356</v>
-      </c>
-      <c r="D444" s="1" t="s">
-        <v>1357</v>
       </c>
       <c r="E444" s="1"/>
       <c r="F444" s="1"/>
       <c r="G444" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H444" s="1"/>
     </row>
@@ -14829,19 +14830,19 @@
       <c r="B445" s="1">
         <v>3</v>
       </c>
-      <c r="C445" s="1" t="s">
-        <v>1359</v>
+      <c r="C445" s="2" t="s">
+        <v>1358</v>
       </c>
       <c r="D445" s="1"/>
       <c r="E445" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F445" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G445" s="1"/>
       <c r="H445" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="446" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14851,19 +14852,19 @@
       <c r="B446" s="1">
         <v>3</v>
       </c>
-      <c r="C446" s="1" t="s">
-        <v>1362</v>
+      <c r="C446" s="2" t="s">
+        <v>1361</v>
       </c>
       <c r="D446" s="1"/>
       <c r="E446" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="F446" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G446" s="1"/>
       <c r="H446" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="447" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -14873,19 +14874,19 @@
       <c r="B447" s="1">
         <v>3</v>
       </c>
-      <c r="C447" s="1" t="s">
-        <v>1365</v>
+      <c r="C447" s="2" t="s">
+        <v>1364</v>
       </c>
       <c r="D447" s="1"/>
       <c r="E447" s="1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F447" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G447" s="1"/>
       <c r="H447" s="1" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="448" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14895,19 +14896,19 @@
       <c r="B448" s="1">
         <v>3</v>
       </c>
-      <c r="C448" s="1" t="s">
-        <v>1368</v>
+      <c r="C448" s="2" t="s">
+        <v>1367</v>
       </c>
       <c r="D448" s="1"/>
       <c r="E448" s="1" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="F448" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G448" s="1"/>
       <c r="H448" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="449" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14917,19 +14918,19 @@
       <c r="B449" s="1">
         <v>3</v>
       </c>
-      <c r="C449" s="1" t="s">
-        <v>1371</v>
+      <c r="C449" s="2" t="s">
+        <v>1370</v>
       </c>
       <c r="D449" s="1"/>
       <c r="E449" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="F449" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G449" s="1"/>
       <c r="H449" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.3">
@@ -14939,19 +14940,19 @@
       <c r="B450" s="1">
         <v>3</v>
       </c>
-      <c r="C450" s="1" t="s">
-        <v>1374</v>
+      <c r="C450" s="2" t="s">
+        <v>1373</v>
       </c>
       <c r="D450" s="1"/>
       <c r="E450" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="F450" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G450" s="1"/>
       <c r="H450" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="451" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14961,19 +14962,19 @@
       <c r="B451" s="1">
         <v>3</v>
       </c>
-      <c r="C451" s="1" t="s">
-        <v>1377</v>
+      <c r="C451" s="2" t="s">
+        <v>1376</v>
       </c>
       <c r="D451" s="1"/>
       <c r="E451" s="1" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="F451" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G451" s="1"/>
       <c r="H451" s="1" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="452" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -14983,19 +14984,19 @@
       <c r="B452" s="1">
         <v>3</v>
       </c>
-      <c r="C452" s="1" t="s">
-        <v>1380</v>
+      <c r="C452" s="2" t="s">
+        <v>1379</v>
       </c>
       <c r="D452" s="1"/>
       <c r="E452" s="1" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="F452" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G452" s="1"/>
       <c r="H452" s="1" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.3">
@@ -15005,19 +15006,19 @@
       <c r="B453" s="1">
         <v>3</v>
       </c>
-      <c r="C453" s="1" t="s">
-        <v>1383</v>
+      <c r="C453" s="2" t="s">
+        <v>1382</v>
       </c>
       <c r="D453" s="1"/>
       <c r="E453" s="1" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="F453" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G453" s="1"/>
       <c r="H453" s="1" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="454" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15027,19 +15028,19 @@
       <c r="B454" s="1">
         <v>3</v>
       </c>
-      <c r="C454" s="1" t="s">
-        <v>1386</v>
+      <c r="C454" s="2" t="s">
+        <v>1385</v>
       </c>
       <c r="D454" s="1"/>
       <c r="E454" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="F454" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G454" s="1"/>
       <c r="H454" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="455" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -15049,19 +15050,19 @@
       <c r="B455" s="1">
         <v>3</v>
       </c>
-      <c r="C455" s="1" t="s">
-        <v>1389</v>
+      <c r="C455" s="2" t="s">
+        <v>1388</v>
       </c>
       <c r="D455" s="1"/>
       <c r="E455" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="F455" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G455" s="1"/>
       <c r="H455" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="456" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -15071,19 +15072,19 @@
       <c r="B456" s="1">
         <v>3</v>
       </c>
-      <c r="C456" s="1" t="s">
-        <v>1392</v>
+      <c r="C456" s="2" t="s">
+        <v>1391</v>
       </c>
       <c r="D456" s="1"/>
       <c r="E456" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="F456" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G456" s="1"/>
       <c r="H456" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="457" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15093,19 +15094,19 @@
       <c r="B457" s="1">
         <v>3</v>
       </c>
-      <c r="C457" s="1" t="s">
-        <v>1395</v>
+      <c r="C457" s="2" t="s">
+        <v>1394</v>
       </c>
       <c r="D457" s="1"/>
       <c r="E457" s="1" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="F457" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G457" s="1"/>
       <c r="H457" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="458" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15115,19 +15116,19 @@
       <c r="B458" s="1">
         <v>3</v>
       </c>
-      <c r="C458" s="1" t="s">
-        <v>1398</v>
+      <c r="C458" s="2" t="s">
+        <v>1397</v>
       </c>
       <c r="D458" s="1"/>
       <c r="E458" s="1" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F458" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G458" s="1"/>
       <c r="H458" s="1" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="459" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15137,19 +15138,19 @@
       <c r="B459" s="1">
         <v>3</v>
       </c>
-      <c r="C459" s="1" t="s">
-        <v>1401</v>
+      <c r="C459" s="2" t="s">
+        <v>1400</v>
       </c>
       <c r="D459" s="1"/>
       <c r="E459" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="F459" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G459" s="1"/>
       <c r="H459" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="460" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15159,19 +15160,19 @@
       <c r="B460" s="1">
         <v>3</v>
       </c>
-      <c r="C460" s="1" t="s">
-        <v>1404</v>
+      <c r="C460" s="2" t="s">
+        <v>1403</v>
       </c>
       <c r="D460" s="1"/>
       <c r="E460" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="F460" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G460" s="1"/>
       <c r="H460" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.3">
@@ -15181,19 +15182,19 @@
       <c r="B461" s="1">
         <v>3</v>
       </c>
-      <c r="C461" s="1" t="s">
-        <v>1407</v>
+      <c r="C461" s="2" t="s">
+        <v>1406</v>
       </c>
       <c r="D461" s="1"/>
       <c r="E461" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="F461" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G461" s="1"/>
       <c r="H461" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.3">
@@ -15203,19 +15204,19 @@
       <c r="B462" s="1">
         <v>3</v>
       </c>
-      <c r="C462" s="1" t="s">
-        <v>1410</v>
+      <c r="C462" s="2" t="s">
+        <v>1409</v>
       </c>
       <c r="D462" s="1"/>
       <c r="E462" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F462" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G462" s="1"/>
       <c r="H462" s="1" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="463" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15225,19 +15226,19 @@
       <c r="B463" s="1">
         <v>3</v>
       </c>
-      <c r="C463" s="1" t="s">
-        <v>1413</v>
+      <c r="C463" s="2" t="s">
+        <v>1412</v>
       </c>
       <c r="D463" s="1"/>
       <c r="E463" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F463" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G463" s="1"/>
       <c r="H463" s="1" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="464" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -15247,19 +15248,19 @@
       <c r="B464" s="1">
         <v>3</v>
       </c>
-      <c r="C464" s="1" t="s">
-        <v>1416</v>
+      <c r="C464" s="2" t="s">
+        <v>1415</v>
       </c>
       <c r="D464" s="1"/>
       <c r="E464" s="1" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F464" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G464" s="1"/>
       <c r="H464" s="1" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="465" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15269,19 +15270,19 @@
       <c r="B465" s="1">
         <v>3</v>
       </c>
-      <c r="C465" s="1" t="s">
-        <v>1419</v>
+      <c r="C465" s="2" t="s">
+        <v>1418</v>
       </c>
       <c r="D465" s="1"/>
       <c r="E465" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F465" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G465" s="1"/>
       <c r="H465" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="466" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15291,19 +15292,19 @@
       <c r="B466" s="1">
         <v>3</v>
       </c>
-      <c r="C466" s="1" t="s">
-        <v>1422</v>
+      <c r="C466" s="2" t="s">
+        <v>1421</v>
       </c>
       <c r="D466" s="1"/>
       <c r="E466" s="1" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="F466" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G466" s="1"/>
       <c r="H466" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="467" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15313,19 +15314,19 @@
       <c r="B467" s="1">
         <v>3</v>
       </c>
-      <c r="C467" s="1" t="s">
-        <v>1425</v>
+      <c r="C467" s="2" t="s">
+        <v>1424</v>
       </c>
       <c r="D467" s="1"/>
       <c r="E467" s="1" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="F467" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G467" s="1"/>
       <c r="H467" s="1" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.3">
@@ -15333,16 +15334,16 @@
       <c r="B468" s="1">
         <v>1</v>
       </c>
-      <c r="C468" s="1" t="s">
+      <c r="C468" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D468" s="1" t="s">
         <v>1428</v>
-      </c>
-      <c r="D468" s="1" t="s">
-        <v>1429</v>
       </c>
       <c r="E468" s="1"/>
       <c r="F468" s="1"/>
       <c r="G468" s="1" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H468" s="1"/>
     </row>
@@ -15351,16 +15352,16 @@
       <c r="B469" s="1">
         <v>2</v>
       </c>
-      <c r="C469" s="1" t="s">
+      <c r="C469" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D469" s="1" t="s">
         <v>1431</v>
-      </c>
-      <c r="D469" s="1" t="s">
-        <v>1432</v>
       </c>
       <c r="E469" s="1"/>
       <c r="F469" s="1"/>
       <c r="G469" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H469" s="1"/>
     </row>
@@ -15371,19 +15372,19 @@
       <c r="B470" s="1">
         <v>3</v>
       </c>
-      <c r="C470" s="1" t="s">
-        <v>1434</v>
+      <c r="C470" s="2" t="s">
+        <v>1433</v>
       </c>
       <c r="D470" s="1"/>
       <c r="E470" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="F470" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G470" s="1"/>
       <c r="H470" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="471" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15393,19 +15394,19 @@
       <c r="B471" s="1">
         <v>3</v>
       </c>
-      <c r="C471" s="1" t="s">
-        <v>1437</v>
+      <c r="C471" s="2" t="s">
+        <v>1436</v>
       </c>
       <c r="D471" s="1"/>
       <c r="E471" s="1" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="F471" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G471" s="1"/>
       <c r="H471" s="1" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="472" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15415,19 +15416,19 @@
       <c r="B472" s="1">
         <v>3</v>
       </c>
-      <c r="C472" s="1" t="s">
-        <v>1440</v>
+      <c r="C472" s="2" t="s">
+        <v>1439</v>
       </c>
       <c r="D472" s="1"/>
       <c r="E472" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F472" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G472" s="1"/>
       <c r="H472" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="473" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -15437,19 +15438,19 @@
       <c r="B473" s="1">
         <v>3</v>
       </c>
-      <c r="C473" s="1" t="s">
-        <v>1443</v>
+      <c r="C473" s="2" t="s">
+        <v>1442</v>
       </c>
       <c r="D473" s="1"/>
       <c r="E473" s="1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="F473" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G473" s="1"/>
       <c r="H473" s="1" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="474" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15459,19 +15460,19 @@
       <c r="B474" s="1">
         <v>3</v>
       </c>
-      <c r="C474" s="1" t="s">
-        <v>1446</v>
+      <c r="C474" s="2" t="s">
+        <v>1445</v>
       </c>
       <c r="D474" s="1"/>
       <c r="E474" s="1" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="F474" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G474" s="1"/>
       <c r="H474" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="475" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15481,19 +15482,19 @@
       <c r="B475" s="1">
         <v>3</v>
       </c>
-      <c r="C475" s="1" t="s">
-        <v>1449</v>
+      <c r="C475" s="2" t="s">
+        <v>1448</v>
       </c>
       <c r="D475" s="1"/>
       <c r="E475" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="F475" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G475" s="1"/>
       <c r="H475" s="1" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.3">
@@ -15501,16 +15502,16 @@
       <c r="B476" s="1">
         <v>2</v>
       </c>
-      <c r="C476" s="1" t="s">
+      <c r="C476" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D476" s="1" t="s">
         <v>1452</v>
-      </c>
-      <c r="D476" s="1" t="s">
-        <v>1453</v>
       </c>
       <c r="E476" s="1"/>
       <c r="F476" s="1"/>
       <c r="G476" s="1" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H476" s="1"/>
     </row>
@@ -15521,19 +15522,19 @@
       <c r="B477" s="1">
         <v>3</v>
       </c>
-      <c r="C477" s="1" t="s">
-        <v>1454</v>
+      <c r="C477" s="2" t="s">
+        <v>1453</v>
       </c>
       <c r="D477" s="1"/>
       <c r="E477" s="1" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F477" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G477" s="1"/>
       <c r="H477" s="1" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="478" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -15543,19 +15544,19 @@
       <c r="B478" s="1">
         <v>3</v>
       </c>
-      <c r="C478" s="1" t="s">
-        <v>1457</v>
+      <c r="C478" s="2" t="s">
+        <v>1456</v>
       </c>
       <c r="D478" s="1"/>
       <c r="E478" s="1" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="F478" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G478" s="1"/>
       <c r="H478" s="1" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="479" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -15565,19 +15566,19 @@
       <c r="B479" s="1">
         <v>3</v>
       </c>
-      <c r="C479" s="1" t="s">
-        <v>1460</v>
+      <c r="C479" s="2" t="s">
+        <v>1459</v>
       </c>
       <c r="D479" s="1"/>
       <c r="E479" s="1" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F479" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G479" s="1"/>
       <c r="H479" s="1" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="480" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15587,19 +15588,19 @@
       <c r="B480" s="1">
         <v>3</v>
       </c>
-      <c r="C480" s="1" t="s">
-        <v>1463</v>
+      <c r="C480" s="2" t="s">
+        <v>1462</v>
       </c>
       <c r="D480" s="1"/>
       <c r="E480" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F480" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G480" s="1"/>
       <c r="H480" s="1" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.3">
@@ -15609,19 +15610,19 @@
       <c r="B481" s="1">
         <v>3</v>
       </c>
-      <c r="C481" s="1" t="s">
-        <v>1466</v>
+      <c r="C481" s="2" t="s">
+        <v>1465</v>
       </c>
       <c r="D481" s="1"/>
       <c r="E481" s="1" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F481" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G481" s="1"/>
       <c r="H481" s="1" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.3">
@@ -15629,16 +15630,16 @@
       <c r="B482" s="1">
         <v>2</v>
       </c>
-      <c r="C482" s="1" t="s">
+      <c r="C482" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D482" s="1" t="s">
         <v>1469</v>
-      </c>
-      <c r="D482" s="1" t="s">
-        <v>1470</v>
       </c>
       <c r="E482" s="1"/>
       <c r="F482" s="1"/>
       <c r="G482" s="1" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H482" s="1"/>
     </row>
@@ -15649,19 +15650,19 @@
       <c r="B483" s="1">
         <v>3</v>
       </c>
-      <c r="C483" s="1" t="s">
-        <v>1472</v>
+      <c r="C483" s="2" t="s">
+        <v>1471</v>
       </c>
       <c r="D483" s="1"/>
       <c r="E483" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="F483" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G483" s="1"/>
       <c r="H483" s="1" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="484" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -15671,19 +15672,19 @@
       <c r="B484" s="1">
         <v>3</v>
       </c>
-      <c r="C484" s="1" t="s">
-        <v>1475</v>
+      <c r="C484" s="2" t="s">
+        <v>1474</v>
       </c>
       <c r="D484" s="1"/>
       <c r="E484" s="1" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="F484" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G484" s="1"/>
       <c r="H484" s="1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="485" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15693,19 +15694,19 @@
       <c r="B485" s="1">
         <v>3</v>
       </c>
-      <c r="C485" s="1" t="s">
-        <v>1478</v>
+      <c r="C485" s="2" t="s">
+        <v>1477</v>
       </c>
       <c r="D485" s="1"/>
       <c r="E485" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="F485" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G485" s="1"/>
       <c r="H485" s="1" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.3">
@@ -15715,19 +15716,19 @@
       <c r="B486" s="1">
         <v>3</v>
       </c>
-      <c r="C486" s="1" t="s">
-        <v>1481</v>
+      <c r="C486" s="2" t="s">
+        <v>1480</v>
       </c>
       <c r="D486" s="1"/>
       <c r="E486" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="F486" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G486" s="1"/>
       <c r="H486" s="1" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.3">
@@ -15735,16 +15736,16 @@
       <c r="B487" s="1">
         <v>2</v>
       </c>
-      <c r="C487" s="1" t="s">
+      <c r="C487" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D487" s="1" t="s">
         <v>1484</v>
-      </c>
-      <c r="D487" s="1" t="s">
-        <v>1485</v>
       </c>
       <c r="E487" s="1"/>
       <c r="F487" s="1"/>
       <c r="G487" s="1" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H487" s="1"/>
     </row>
@@ -15755,19 +15756,19 @@
       <c r="B488" s="1">
         <v>3</v>
       </c>
-      <c r="C488" s="1" t="s">
-        <v>1487</v>
+      <c r="C488" s="2" t="s">
+        <v>1486</v>
       </c>
       <c r="D488" s="1"/>
       <c r="E488" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F488" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G488" s="1"/>
       <c r="H488" s="1" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="489" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -15777,19 +15778,19 @@
       <c r="B489" s="1">
         <v>3</v>
       </c>
-      <c r="C489" s="1" t="s">
-        <v>1490</v>
+      <c r="C489" s="2" t="s">
+        <v>1489</v>
       </c>
       <c r="D489" s="1"/>
       <c r="E489" s="1" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F489" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G489" s="1"/>
       <c r="H489" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.3">
@@ -15797,16 +15798,16 @@
       <c r="B490" s="1">
         <v>2</v>
       </c>
-      <c r="C490" s="1" t="s">
+      <c r="C490" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D490" s="1" t="s">
         <v>1493</v>
-      </c>
-      <c r="D490" s="1" t="s">
-        <v>1494</v>
       </c>
       <c r="E490" s="1"/>
       <c r="F490" s="1"/>
       <c r="G490" s="1" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H490" s="1"/>
     </row>
@@ -15817,19 +15818,19 @@
       <c r="B491" s="1">
         <v>3</v>
       </c>
-      <c r="C491" s="1" t="s">
-        <v>1495</v>
+      <c r="C491" s="2" t="s">
+        <v>1494</v>
       </c>
       <c r="D491" s="1"/>
       <c r="E491" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="F491" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G491" s="1"/>
       <c r="H491" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="492" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -15839,19 +15840,19 @@
       <c r="B492" s="1">
         <v>3</v>
       </c>
-      <c r="C492" s="1" t="s">
-        <v>1498</v>
+      <c r="C492" s="2" t="s">
+        <v>1497</v>
       </c>
       <c r="D492" s="1"/>
       <c r="E492" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="F492" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G492" s="1"/>
       <c r="H492" s="1" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="493" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -15861,23 +15862,26 @@
       <c r="B493" s="1">
         <v>3</v>
       </c>
-      <c r="C493" s="1" t="s">
-        <v>1501</v>
+      <c r="C493" s="2" t="s">
+        <v>1500</v>
       </c>
       <c r="D493" s="1"/>
       <c r="E493" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="F493" s="1" t="s">
         <v>256</v>
       </c>
       <c r="G493" s="1"/>
       <c r="H493" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="C2:C493" numberStoredAsText="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -15940,10 +15944,10 @@
         <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>1504</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -15951,10 +15955,10 @@
         <v>248</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -15962,10 +15966,10 @@
         <v>354</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>1508</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -15973,10 +15977,10 @@
         <v>256</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>1510</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1511</v>
       </c>
     </row>
   </sheetData>
